--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -890,7 +890,7 @@
         <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
         <v>1.78</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
         <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
         <v>16.5</v>
@@ -2701,7 +2701,7 @@
         <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
         <v>9.4</v>
@@ -2710,7 +2710,7 @@
         <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
         <v>29</v>
@@ -2719,22 +2719,22 @@
         <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
         <v>65</v>
@@ -2752,10 +2752,10 @@
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>6.4</v>
@@ -2764,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
@@ -2776,25 +2776,25 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF9" t="n">
         <v>5</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
         <v>4.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I13" t="n">
         <v>2.28</v>
@@ -3666,7 +3666,7 @@
         <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
         <v>1.96</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>6.6</v>
       </c>
       <c r="G14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>1.55</v>
       </c>
       <c r="I14" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
         <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U15" t="n">
         <v>1.9</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
         <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89</v>
+        <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G18" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>1.85</v>
@@ -2701,7 +2701,7 @@
         <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
         <v>9.4</v>
@@ -2716,7 +2716,7 @@
         <v>29</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH9" t="n">
         <v>25</v>
@@ -2728,37 +2728,37 @@
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
         <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
         <v>10</v>
@@ -2767,34 +2767,34 @@
         <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
         <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
         <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
         <v>5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
         <v>4.6</v>
@@ -3663,7 +3663,7 @@
         <v>2.28</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.95</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="G14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="I14" t="n">
         <v>1.69</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
         <v>4.3</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
         <v>2.28</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
         <v>4.9</v>
@@ -4171,10 +4171,10 @@
         <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
         <v>1.9</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
         <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -860,13 +860,13 @@
         <v>1.87</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
@@ -1377,7 +1377,7 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
         <v>1.78</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
         <v>16.5</v>
@@ -2701,16 +2701,16 @@
         <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
         <v>29</v>
@@ -2719,43 +2719,43 @@
         <v>18.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
         <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
         <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
@@ -2764,37 +2764,37 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
         <v>4.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="I14" t="n">
         <v>1.69</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
         <v>2.08</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4213,112 +4213,112 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
         <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
         <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
         <v>100</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
         <v>170</v>
       </c>
       <c r="AN15" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
         <v>130</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
         <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT15" t="n">
         <v>6.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.14</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>4.3</v>
@@ -4428,7 +4428,7 @@
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
         <v>2.12</v>
@@ -4682,7 +4682,7 @@
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
         <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H18" t="n">
         <v>3.5</v>
@@ -4933,7 +4933,7 @@
         <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -866,7 +866,7 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -875,16 +875,16 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
         <v>1.7</v>
@@ -893,194 +893,194 @@
         <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1129,16 +1129,16 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.02</v>
@@ -1147,194 +1147,194 @@
         <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1377,218 +1377,218 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
         <v>3.65</v>
@@ -2644,7 +2644,7 @@
         <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
@@ -2680,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
         <v>16.5</v>
@@ -2704,7 +2704,7 @@
         <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>14</v>
@@ -2752,10 +2752,10 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
@@ -2764,10 +2764,10 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2776,22 +2776,22 @@
         <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
         <v>4.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I14" t="n">
         <v>1.69</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
         <v>160</v>
@@ -4252,7 +4252,7 @@
         <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>55</v>
@@ -4273,10 +4273,10 @@
         <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT15" t="n">
         <v>6.6</v>
@@ -4285,22 +4285,22 @@
         <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB15" t="n">
         <v>15</v>
@@ -4309,16 +4309,16 @@
         <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
         <v>2.28</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="G18" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H18" t="n">
         <v>3.5</v>
@@ -4933,7 +4933,7 @@
         <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -866,16 +866,16 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -887,31 +887,31 @@
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
         <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
         <v>17.5</v>
@@ -923,7 +923,7 @@
         <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>9.6</v>
@@ -935,7 +935,7 @@
         <v>90</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -950,13 +950,13 @@
         <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
         <v>22</v>
@@ -965,7 +965,7 @@
         <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>10.5</v>
@@ -995,7 +995,7 @@
         <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>1.01</v>
@@ -1004,7 +1004,7 @@
         <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>1.01</v>
@@ -1013,74 +1013,74 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
@@ -1129,212 +1129,212 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.14</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.42</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
         <v>970</v>
       </c>
-      <c r="Z3" t="n">
-        <v>21</v>
-      </c>
       <c r="AA3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK3" t="n">
         <v>44</v>
       </c>
-      <c r="AB3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN3" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
@@ -1377,13 +1377,13 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1392,7 +1392,7 @@
         <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
         <v>1.93</v>
@@ -1401,10 +1401,10 @@
         <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1422,7 +1422,7 @@
         <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1431,7 +1431,7 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
@@ -1485,10 +1485,10 @@
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
@@ -1497,22 +1497,22 @@
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1527,68 +1527,68 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="BP4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
         <v>1.17</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
         <v>3.65</v>
@@ -2644,55 +2644,55 @@
         <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
         <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
         <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
         <v>16.5</v>
@@ -2704,7 +2704,7 @@
         <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
         <v>14</v>
@@ -2713,7 +2713,7 @@
         <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
         <v>18.5</v>
@@ -2728,7 +2728,7 @@
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
         <v>80</v>
@@ -2746,119 +2746,119 @@
         <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA9" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -3409,218 +3409,218 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="G14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="I14" t="n">
         <v>1.69</v>
@@ -3920,7 +3920,7 @@
         <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>170</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
         <v>130</v>
@@ -4273,10 +4273,10 @@
         <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>6.6</v>
@@ -4285,22 +4285,22 @@
         <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB15" t="n">
         <v>15</v>
@@ -4309,16 +4309,16 @@
         <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
         <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>2.16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
         <v>2.42</v>
@@ -4954,7 +4954,7 @@
         <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 09:38:18</t>
+          <t>2026-06-05 11:50:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -1022,7 +1022,7 @@
         <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1144,7 +1144,7 @@
         <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1410,7 +1410,7 @@
         <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V4" t="n">
         <v>1.19</v>
@@ -1446,7 +1446,7 @@
         <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
         <v>26</v>
@@ -1461,13 +1461,13 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>120</v>
@@ -1485,10 +1485,10 @@
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
@@ -1500,7 +1500,7 @@
         <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
@@ -1512,7 +1512,7 @@
         <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1530,7 +1530,7 @@
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
         <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5" t="n">
         <v>1.02</v>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
         <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
         <v>1.02</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.17</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
         <v>1.02</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.17</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
         <v>1.02</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
         <v>2.46</v>
@@ -2665,10 +2665,10 @@
         <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
@@ -2677,10 +2677,10 @@
         <v>4.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
         <v>1.69</v>
@@ -2692,7 +2692,7 @@
         <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
         <v>16.5</v>
@@ -2701,19 +2701,19 @@
         <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG9" t="n">
         <v>18.5</v>
@@ -2728,22 +2728,22 @@
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
         <v>6</v>
@@ -2752,46 +2752,46 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.9</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
@@ -2800,19 +2800,19 @@
         <v>2.92</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN9" t="n">
         <v>6.8</v>
@@ -2824,13 +2824,13 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
         <v>5.1</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10" t="n">
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J10" t="n">
         <v>1.02</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
@@ -2928,7 +2928,7 @@
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
         <v>1.02</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.24</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12" t="n">
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J12" t="n">
         <v>1.02</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
@@ -3436,7 +3436,7 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>1.43</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="I14" t="n">
-        <v>1.69</v>
+        <v>2.28</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,42 +4145,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>7.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>10.5</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>1.58</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>1.66</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4213,112 +4213,112 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,37 +4404,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,112 +4467,112 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,261 +4890,515 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:02:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>18:30:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Defensor Sporting</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Boston River</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G19" t="n">
         <v>2.42</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>3.5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>5.2</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>2.96</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>3.6</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-06-05 11:50:17</t>
+      <c r="Q19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -896,7 +896,7 @@
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
         <v>1.92</v>
@@ -1022,7 +1022,7 @@
         <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
         <v>2.18</v>
@@ -1123,7 +1123,7 @@
         <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
@@ -1159,7 +1159,7 @@
         <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W3" t="n">
         <v>1.37</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
@@ -1383,7 +1383,7 @@
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1398,7 +1398,7 @@
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1461,7 +1461,7 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>150</v>
@@ -1494,7 +1494,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
@@ -1506,7 +1506,7 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
         <v>13</v>
@@ -1530,7 +1530,7 @@
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
         <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
         <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1903,13 +1903,13 @@
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
         <v>1.17</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
         <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q7" t="n">
         <v>1.17</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
         <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2644,13 @@
         <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2695,7 +2695,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
         <v>40</v>
@@ -2704,13 +2704,13 @@
         <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
         <v>27</v>
@@ -2728,10 +2728,10 @@
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
@@ -2746,7 +2746,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
@@ -2764,34 +2764,34 @@
         <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
         <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
         <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3194,7 +3194,7 @@
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
         <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3675,10 +3675,10 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
         <v>2.92</v>
@@ -3696,7 +3696,7 @@
         <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
@@ -3705,109 +3705,109 @@
         <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>18</v>
       </c>
-      <c r="AG13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>21</v>
-      </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3923,16 +3923,16 @@
         <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
         <v>1.83</v>
@@ -3941,194 +3941,194 @@
         <v>1.96</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -4159,237 +4159,237 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G15" t="n">
         <v>10.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="I15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>1.21</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,37 +4658,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="H17" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4709,10 +4709,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4721,112 +4721,112 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,498 +4907,752 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:14:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>18:30:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Defensor Sporting</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Boston River</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>2.04</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>2.42</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>3.5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>5.2</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2.96</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>3.6</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>2026-06-05 14:02:16</t>
+      <c r="Q20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -890,13 +890,13 @@
         <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
         <v>1.92</v>
@@ -905,7 +905,7 @@
         <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
         <v>1.94</v>
@@ -1022,7 +1022,7 @@
         <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
@@ -1377,13 +1377,13 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1398,7 +1398,7 @@
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1407,7 +1407,7 @@
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>1.97</v>
@@ -1530,7 +1530,7 @@
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1903,13 +1903,13 @@
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
         <v>1.17</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2800,7 +2800,7 @@
         <v>2.92</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>2.04</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
@@ -3708,7 +3708,7 @@
         <v>42</v>
       </c>
       <c r="Y13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z13" t="n">
         <v>80</v>
@@ -3717,13 +3717,13 @@
         <v>200</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
         <v>16.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE13" t="n">
         <v>90</v>
@@ -3750,10 +3750,10 @@
         <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO13" t="n">
         <v>70</v>
@@ -3771,19 +3771,19 @@
         <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
@@ -3798,7 +3798,7 @@
         <v>10.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
         <v>18</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
         <v>4.6</v>
@@ -3935,7 +3935,7 @@
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>1.96</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>10.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="I15" t="n">
         <v>1.67</v>
@@ -4177,13 +4177,13 @@
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
         <v>1.43</v>
@@ -4330,31 +4330,31 @@
         <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
         <v>12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>3.9</v>
@@ -4366,23 +4366,23 @@
         <v>11.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.46</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q16" t="n">
         <v>1.21</v>
@@ -4452,7 +4452,7 @@
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4521,52 +4521,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
         <v>2.08</v>
@@ -4712,7 +4712,7 @@
         <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -4924,31 +4924,31 @@
         <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
         <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>1.76</v>
+        <v>2.76</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
         <v>1.75</v>
@@ -4963,142 +4963,142 @@
         <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
         <v>1.81</v>
-      </c>
-      <c r="X18" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
         <v>14.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.8</v>
+        <v>1.61</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>21</v>
+        <v>1.81</v>
       </c>
       <c r="BN18" t="n">
         <v>6.4</v>
@@ -5110,13 +5110,13 @@
         <v>23</v>
       </c>
       <c r="BQ18" t="n">
-        <v>11</v>
+        <v>1.68</v>
       </c>
       <c r="BR18" t="n">
         <v>48</v>
       </c>
       <c r="BS18" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BT18" t="n">
         <v>9.6</v>
@@ -5128,23 +5128,23 @@
         <v>50</v>
       </c>
       <c r="BW18" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BZ18" t="n">
         <v>48</v>
       </c>
       <c r="CA18" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -5193,16 +5193,16 @@
         <v>7.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -5211,184 +5211,184 @@
         <v>1.54</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="G20" t="n">
         <v>2.42</v>
@@ -5462,7 +5462,7 @@
         <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 16:14:13</t>
+          <t>2026-06-05 18:26:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -866,31 +866,31 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
@@ -899,10 +899,10 @@
         <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.23</v>
@@ -959,7 +959,7 @@
         <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
         <v>120</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>3.75</v>
@@ -1126,7 +1126,7 @@
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.32</v>
@@ -1135,16 +1135,16 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
@@ -1153,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
         <v>2.42</v>
@@ -1177,7 +1177,7 @@
         <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>9.800000000000001</v>
@@ -1276,19 +1276,19 @@
         <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>970</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>6.8</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>5.4</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
@@ -1374,16 +1374,16 @@
         <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1392,28 +1392,28 @@
         <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
         <v>2.28</v>
@@ -1425,40 +1425,40 @@
         <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1506,7 +1506,7 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
         <v>13</v>
@@ -1527,7 +1527,7 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI4" t="n">
         <v>2.8</v>
@@ -1536,16 +1536,16 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4" t="n">
         <v>3.35</v>
@@ -1554,41 +1554,41 @@
         <v>970</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1658,7 +1658,7 @@
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1903,13 +1903,13 @@
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
         <v>1.17</v>
@@ -1921,7 +1921,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.17</v>
@@ -2166,7 +2166,7 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
         <v>3.6</v>
@@ -2806,7 +2806,7 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>5.1</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
@@ -2931,16 +2931,16 @@
         <v>1.23</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
         <v>1.24</v>
@@ -3436,7 +3436,7 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
         <v>1.53</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H14" t="n">
         <v>2.02</v>
@@ -3917,40 +3917,40 @@
         <v>2.28</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,91 +3959,91 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
@@ -4061,16 +4061,16 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4100,7 +4100,7 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BT14" t="n">
         <v>5.2</v>
@@ -4109,26 +4109,26 @@
         <v>3.95</v>
       </c>
       <c r="BV14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>10.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I15" t="n">
         <v>1.67</v>
@@ -4198,7 +4198,7 @@
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
         <v>2.28</v>
@@ -4324,7 +4324,7 @@
         <v>3.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="BJ15" t="n">
         <v>13.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.21</v>
@@ -4452,7 +4452,7 @@
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>1.21</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4921,91 +4921,91 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>75</v>
@@ -5014,73 +5014,73 @@
         <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA18" t="n">
+      <c r="BF18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG18" t="n">
         <v>55</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>46</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H19" t="n">
         <v>3.65</v>
@@ -5190,7 +5190,7 @@
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,10 +5199,10 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.44</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -5211,82 +5211,82 @@
         <v>1.54</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>25</v>
       </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>30</v>
-      </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
         <v>1.03</v>
@@ -5295,34 +5295,34 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
         <v>1.03</v>
@@ -5331,10 +5331,10 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BH19" t="n">
         <v>5.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -5429,34 +5429,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
         <v>1.68</v>
@@ -5465,194 +5465,194 @@
         <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -863,40 +863,40 @@
         <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
         <v>1.93</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
         <v>3.75</v>
@@ -1120,7 +1120,7 @@
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
@@ -1159,7 +1159,7 @@
         <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.37</v>
@@ -1270,13 +1270,13 @@
         <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
         <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
         <v>1.85</v>
@@ -1413,7 +1413,7 @@
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
         <v>2.28</v>
@@ -1431,7 +1431,7 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
@@ -1455,10 +1455,10 @@
         <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1494,7 +1494,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
@@ -1530,7 +1530,7 @@
         <v>3.55</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
@@ -1915,10 +1915,10 @@
         <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
@@ -2166,13 +2166,13 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.02</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
@@ -2423,16 +2423,16 @@
         <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2641,16 +2641,16 @@
         <v>3.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.52</v>
@@ -2668,7 +2668,7 @@
         <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
@@ -2680,7 +2680,7 @@
         <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
         <v>1.69</v>
@@ -2689,13 +2689,13 @@
         <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA9" t="n">
         <v>40</v>
@@ -2704,7 +2704,7 @@
         <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
@@ -2737,7 +2737,7 @@
         <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
         <v>34</v>
@@ -2758,61 +2758,61 @@
         <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>8.6</v>
       </c>
       <c r="AW9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.3</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF9" t="n">
         <v>5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
         <v>6.8</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>11</v>
       </c>
-      <c r="BT9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3149,14 +3149,14 @@
         <v>1000</v>
       </c>
       <c r="H11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.09</v>
       </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="K11" t="n">
         <v>1000</v>
       </c>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.15</v>
@@ -3182,16 +3182,16 @@
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -3439,10 +3439,10 @@
         <v>1.23</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G13" t="n">
         <v>1.53</v>
@@ -3669,7 +3669,7 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3690,7 +3690,7 @@
         <v>1.78</v>
       </c>
       <c r="S13" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="T13" t="n">
         <v>1.61</v>
@@ -3813,68 +3813,68 @@
         <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BQ13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU13" t="n">
         <v>5.4</v>
       </c>
-      <c r="BR13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.78</v>
+        <v>8.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.42</v>
+        <v>5.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3905,52 +3905,52 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J14" t="n">
         <v>3.45</v>
       </c>
-      <c r="G14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,28 +3959,28 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
         <v>11.5</v>
       </c>
       <c r="Z14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB14" t="n">
         <v>16</v>
       </c>
-      <c r="AA14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
         <v>32</v>
@@ -3998,22 +3998,22 @@
         <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
         <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
         <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>7.6</v>
@@ -4022,25 +4022,25 @@
         <v>10.5</v>
       </c>
       <c r="AS14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX14" t="n">
         <v>20</v>
       </c>
-      <c r="AT14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>21</v>
-      </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>13.5</v>
@@ -4064,13 +4064,13 @@
         <v>34</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4088,13 +4088,13 @@
         <v>7.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4103,32 +4103,32 @@
         <v>30</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BZ14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4177,25 +4177,25 @@
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
@@ -4216,37 +4216,37 @@
         <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AB15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
         <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>85</v>
       </c>
       <c r="AG15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
         <v>400</v>
@@ -4264,13 +4264,13 @@
         <v>400</v>
       </c>
       <c r="AO15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AR15" t="n">
         <v>6.2</v>
@@ -4291,7 +4291,7 @@
         <v>16</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
         <v>1.03</v>
@@ -4300,7 +4300,7 @@
         <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB15" t="n">
         <v>1.01</v>
@@ -4321,7 +4321,7 @@
         <v>10</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI15" t="n">
         <v>2.66</v>
@@ -4330,7 +4330,7 @@
         <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,47 +4342,47 @@
         <v>12</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT15" t="n">
         <v>3.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BV15" t="n">
         <v>11.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
         <v>1.21</v>
@@ -4455,10 +4455,10 @@
         <v>1.21</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.12</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
         <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
         <v>130</v>
@@ -4796,7 +4796,7 @@
         <v>4.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>8</v>
@@ -4805,10 +4805,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
         <v>15</v>
@@ -4817,10 +4817,10 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
         <v>11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H19" t="n">
         <v>3.65</v>
@@ -5193,7 +5193,7 @@
         <v>5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -5217,16 +5217,16 @@
         <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
         <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X19" t="n">
         <v>27</v>
@@ -5253,7 +5253,7 @@
         <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
@@ -5277,22 +5277,22 @@
         <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
         <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
         <v>1.01</v>
@@ -5304,7 +5304,7 @@
         <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
         <v>1.01</v>
@@ -5316,7 +5316,7 @@
         <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
         <v>1.01</v>
@@ -5325,70 +5325,70 @@
         <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>2.44</v>
+        <v>1.06</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -5432,37 +5432,37 @@
         <v>2.06</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H20" t="n">
         <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K20" t="n">
         <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
         <v>1.25</v>
@@ -5477,22 +5477,22 @@
         <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
         <v>9.6</v>
@@ -5501,10 +5501,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="n">
         <v>15</v>
@@ -5516,7 +5516,7 @@
         <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ20" t="n">
         <v>34</v>
@@ -5528,34 +5528,34 @@
         <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN20" t="n">
         <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="n">
         <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS20" t="n">
         <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
         <v>1.01</v>
@@ -5564,19 +5564,19 @@
         <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
         <v>1.01</v>
@@ -5585,74 +5585,74 @@
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO20" t="n">
         <v>3.6</v>
       </c>
-      <c r="BI20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BP20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -881,22 +881,22 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.93</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
@@ -1141,10 +1141,10 @@
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
@@ -1159,7 +1159,7 @@
         <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W3" t="n">
         <v>1.37</v>
@@ -1276,10 +1276,10 @@
         <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="BK3" t="n">
         <v>5.3</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
         <v>1.85</v>
@@ -1413,7 +1413,7 @@
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
         <v>2.28</v>
@@ -1431,7 +1431,7 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
@@ -1530,7 +1530,7 @@
         <v>3.55</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1643,34 +1643,34 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1924,7 +1924,7 @@
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2776,7 +2776,7 @@
         <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
         <v>5.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2880,28 +2880,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3134,55 +3134,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.25</v>
       </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Q11" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3308,65 +3308,65 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3421,16 +3421,16 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
         <v>1.53</v>
@@ -3660,7 +3660,7 @@
         <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -3669,7 +3669,7 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3681,31 +3681,31 @@
         <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
         <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y13" t="n">
         <v>44</v>
@@ -3717,7 +3717,7 @@
         <v>200</v>
       </c>
       <c r="AB13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC13" t="n">
         <v>16.5</v>
@@ -3741,16 +3741,16 @@
         <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
         <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
         <v>5.5</v>
@@ -3807,74 +3807,74 @@
         <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG13" t="n">
         <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>10</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>9.6</v>
       </c>
       <c r="BN13" t="n">
         <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
         <v>11</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>10.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3905,52 +3905,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
         <v>4.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I14" t="n">
         <v>2.36</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.31</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,19 +3959,19 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
         <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC14" t="n">
         <v>9.199999999999999</v>
@@ -3980,7 +3980,7 @@
         <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF14" t="n">
         <v>32</v>
@@ -3992,7 +3992,7 @@
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
         <v>85</v>
@@ -4007,16 +4007,16 @@
         <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
@@ -4025,16 +4025,16 @@
         <v>21</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX14" t="n">
         <v>20</v>
@@ -4061,28 +4061,28 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>7.4</v>
@@ -4094,13 +4094,13 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>30</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>5.3</v>
@@ -4109,26 +4109,26 @@
         <v>4</v>
       </c>
       <c r="BV14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         <v>3.05</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="BJ15" t="n">
         <v>13.5</v>
@@ -4360,7 +4360,7 @@
         <v>3.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BV15" t="n">
         <v>11.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q16" t="n">
         <v>1.21</v>
@@ -4578,65 +4578,65 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
         <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP17" t="n">
         <v>9.199999999999999</v>
@@ -4781,10 +4781,10 @@
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4960,7 +4960,7 @@
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.89</v>
@@ -5083,68 +5083,68 @@
         <v>55</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.81</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.81</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.68</v>
+        <v>13</v>
       </c>
       <c r="BR18" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="BT18" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
         <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
         <v>5.4</v>
@@ -5295,7 +5295,7 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
         <v>1.01</v>
@@ -5331,7 +5331,7 @@
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
@@ -5382,13 +5382,13 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.06</v>
       </c>
       <c r="G20" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
         <v>3.9</v>
@@ -5441,7 +5441,7 @@
         <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3.6</v>
@@ -5474,7 +5474,7 @@
         <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
         <v>1.28</v>
@@ -5489,10 +5489,10 @@
         <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
         <v>9.6</v>
@@ -5540,13 +5540,13 @@
         <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR20" t="n">
         <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -5555,40 +5555,40 @@
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
         <v>3.05</v>
@@ -5597,10 +5597,10 @@
         <v>2.48</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK20" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,7 +5612,7 @@
         <v>4.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -863,22 +863,22 @@
         <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
         <v>3.1</v>
@@ -893,10 +893,10 @@
         <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
         <v>1.93</v>
@@ -971,10 +971,10 @@
         <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
         <v>5.8</v>
@@ -986,7 +986,7 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
@@ -998,7 +998,7 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -1007,22 +1007,22 @@
         <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>3.75</v>
@@ -1141,13 +1141,13 @@
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1174,7 +1174,7 @@
         <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
@@ -1189,7 +1189,7 @@
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1207,7 +1207,7 @@
         <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
         <v>95</v>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1240,10 +1240,10 @@
         <v>8.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1252,25 +1252,25 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
         <v>3.75</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
         <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1395,16 +1395,16 @@
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.85</v>
@@ -1419,28 +1419,28 @@
         <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
@@ -1449,7 +1449,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>95</v>
@@ -1464,13 +1464,13 @@
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="n">
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
@@ -1479,22 +1479,22 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
@@ -1506,52 +1506,52 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.55</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>6.2</v>
@@ -1560,35 +1560,35 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2704,13 +2704,13 @@
         <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
         <v>27</v>
@@ -2722,13 +2722,13 @@
         <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
         <v>65</v>
@@ -2767,13 +2767,13 @@
         <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA9" t="n">
         <v>44</v>
@@ -2785,13 +2785,13 @@
         <v>4.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
@@ -2836,7 +2836,7 @@
         <v>5</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I13" t="n">
         <v>7.6</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -3672,49 +3672,49 @@
         <v>1.19</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
         <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X13" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
         <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB13" t="n">
         <v>17.5</v>
@@ -3726,7 +3726,7 @@
         <v>34</v>
       </c>
       <c r="AE13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
@@ -3753,46 +3753,46 @@
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO13" t="n">
         <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU13" t="n">
         <v>10</v>
       </c>
-      <c r="AU13" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
         <v>10.5</v>
@@ -3804,19 +3804,19 @@
         <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.800000000000001</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
         <v>4.7</v>
@@ -3843,16 +3843,16 @@
         <v>5</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS13" t="n">
         <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
         <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
         <v>120</v>
@@ -4016,7 +4016,7 @@
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
@@ -4049,19 +4049,19 @@
         <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
         <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
         <v>14</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BN14" t="n">
         <v>7.4</v>
@@ -4094,13 +4094,13 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
         <v>5.3</v>
@@ -4112,23 +4112,23 @@
         <v>17.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>1.54</v>
       </c>
       <c r="I15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
@@ -4183,7 +4183,7 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
         <v>1.44</v>
@@ -4195,7 +4195,7 @@
         <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
@@ -4225,7 +4225,7 @@
         <v>16</v>
       </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
         <v>9.6</v>
@@ -4237,10 +4237,10 @@
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AG15" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
         <v>34</v>
@@ -4264,7 +4264,7 @@
         <v>400</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
         <v>8.4</v>
@@ -4291,31 +4291,31 @@
         <v>16</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA15" t="n">
         <v>42</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
         <v>3.05</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
         <v>13.5</v>
@@ -4360,7 +4360,7 @@
         <v>3.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BV15" t="n">
         <v>11.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q16" t="n">
         <v>1.21</v>
@@ -4521,52 +4521,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
         <v>1.92</v>
@@ -4727,7 +4727,7 @@
         <v>19</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="n">
         <v>160</v>
@@ -4742,7 +4742,7 @@
         <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF17" t="n">
         <v>11.5</v>
@@ -4766,7 +4766,7 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="n">
         <v>970</v>
@@ -4793,7 +4793,7 @@
         <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
         <v>2.22</v>
@@ -4954,7 +4954,7 @@
         <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -4969,7 +4969,7 @@
         <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
         <v>1.81</v>
@@ -4978,7 +4978,7 @@
         <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
         <v>27</v>
@@ -4987,7 +4987,7 @@
         <v>90</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
         <v>7.4</v>
@@ -5008,7 +5008,7 @@
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
         <v>30</v>
@@ -5038,7 +5038,7 @@
         <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -5050,7 +5050,7 @@
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5062,19 +5062,19 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BB18" t="n">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD18" t="n">
         <v>40</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
         <v>20</v>
@@ -5092,7 +5092,7 @@
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,13 +5104,13 @@
         <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP18" t="n">
         <v>18</v>
       </c>
       <c r="BQ18" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -5175,34 +5175,34 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G19" t="n">
         <v>2.02</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
         <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -5223,16 +5223,16 @@
         <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
         <v>1.98</v>
       </c>
       <c r="X19" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
         <v>44</v>
@@ -5247,7 +5247,7 @@
         <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
         <v>60</v>
@@ -5259,7 +5259,7 @@
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
         <v>60</v>
@@ -5280,61 +5280,61 @@
         <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
         <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
@@ -5594,13 +5594,13 @@
         <v>3.05</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20" t="n">
         <v>970</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,7 +5612,7 @@
         <v>4.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -1102,239 +1102,239 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon FC</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X3" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="AS3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="BG3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BT3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU3" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>950</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>8.4</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>8</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -1356,187 +1356,187 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Seoul E-Land FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju FC</t>
+          <t>Suwon FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>2.46</v>
       </c>
       <c r="J4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH4" t="n">
         <v>3.75</v>
       </c>
-      <c r="K4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="BI4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>950</v>
       </c>
-      <c r="AE4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,40 +1545,40 @@
         <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Seoul E-Land FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Cheongju FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.06</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1924,7 +1924,7 @@
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2432,7 +2432,7 @@
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>1.06</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>1.22</v>
       </c>
       <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.23</v>
       </c>
-      <c r="S9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.25</v>
       </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -3134,28 +3134,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3424,19 +3424,19 @@
         <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
         <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>1.06</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.02</v>
       </c>
-      <c r="N13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.15</v>
-      </c>
       <c r="W13" t="n">
-        <v>2.92</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR14" t="n">
         <v>4.4</v>
       </c>
-      <c r="H14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AS14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT14" t="n">
         <v>11</v>
       </c>
-      <c r="Z14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
+      <c r="BU14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CA14" t="n">
         <v>7</v>
       </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>7.4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="AR15" t="n">
         <v>10.5</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AS15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
         <v>8.4</v>
       </c>
-      <c r="AA15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="AW15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX15" t="n">
         <v>34</v>
       </c>
-      <c r="AI15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>400</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>400</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="BY15" t="n">
         <v>7</v>
       </c>
-      <c r="AY15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="G16" t="n">
-        <v>1.74</v>
+        <v>10.5</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="J16" t="n">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.34</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.21</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>1.21</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="G18" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
         <v>11</v>
       </c>
-      <c r="Y18" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BF18" t="n">
         <v>11</v>
       </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>20</v>
-      </c>
       <c r="BG18" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.54</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
         <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA19" t="n">
         <v>60</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="BB19" t="n">
         <v>25</v>
       </c>
-      <c r="AK19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,244 +5415,752 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>3.9</v>
       </c>
       <c r="I20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
         <v>4.7</v>
       </c>
-      <c r="J20" t="n">
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-06 05:26:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Uruguay Montevideo FC</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
         <v>3</v>
       </c>
-      <c r="K20" t="n">
+      <c r="BI21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-06 05:26:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.6</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L22" t="n">
         <v>1.41</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M22" t="n">
         <v>1.1</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N22" t="n">
         <v>2.96</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O22" t="n">
         <v>1.43</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P22" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q22" t="n">
         <v>2.26</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R22" t="n">
         <v>1.25</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S22" t="n">
         <v>4.3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>1.79</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>1.77</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V22" t="n">
         <v>1.28</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W22" t="n">
         <v>1.82</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X22" t="n">
         <v>13</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y22" t="n">
         <v>15</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z22" t="n">
         <v>36</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA22" t="n">
         <v>120</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AB22" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC22" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AD22" t="n">
         <v>22</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE22" t="n">
         <v>80</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AF22" t="n">
         <v>15</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AG22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH22" t="n">
         <v>26</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AI22" t="n">
         <v>95</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AJ22" t="n">
         <v>34</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK22" t="n">
         <v>32</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AL22" t="n">
         <v>60</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AM22" t="n">
         <v>180</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AN22" t="n">
         <v>27</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AO22" t="n">
         <v>110</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AP22" t="n">
         <v>8</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ22" t="n">
         <v>3.55</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR22" t="n">
         <v>21</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AS22" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AT22" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AU22" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AV22" t="n">
         <v>3.85</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AW22" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AX22" t="n">
         <v>3.55</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AY22" t="n">
         <v>3.45</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="AZ22" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BA22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB22" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BC22" t="n">
         <v>4</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BD22" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BE22" t="n">
         <v>4.6</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BF22" t="n">
         <v>3.95</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BG22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BH22" t="n">
         <v>3.05</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BI22" t="n">
         <v>2.72</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BJ22" t="n">
         <v>970</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BK22" t="n">
         <v>6</v>
       </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
         <v>3.25</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BN22" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BO22" t="n">
         <v>3.6</v>
       </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
         <v>7.4</v>
       </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="BT22" t="n">
         <v>7.6</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="BU22" t="n">
         <v>5.6</v>
       </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
         <v>8.6</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
         <v>3.3</v>
       </c>
-      <c r="BZ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA20" t="n">
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
         <v>8.4</v>
       </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-06-06 03:14:35</t>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H2" t="n">
         <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1028,59 +1028,59 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
@@ -1144,19 +1144,19 @@
         <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
         <v>1.23</v>
@@ -1294,7 +1294,7 @@
         <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
         <v>3.75</v>
@@ -1380,34 +1380,34 @@
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
         <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
         <v>2.42</v>
@@ -1434,7 +1434,7 @@
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
@@ -1455,10 +1455,10 @@
         <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
         <v>50</v>
@@ -1482,7 +1482,7 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
@@ -1494,10 +1494,10 @@
         <v>8.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1506,43 +1506,43 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="BN4" t="n">
         <v>6.8</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BT4" t="n">
         <v>5.4</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
         <v>1.91</v>
@@ -1628,13 +1628,13 @@
         <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1652,13 +1652,13 @@
         <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
         <v>1.85</v>
@@ -1781,25 +1781,25 @@
         <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO5" t="n">
         <v>3.4</v>
@@ -1808,41 +1808,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1897,19 +1897,19 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
         <v>1.17</v>
@@ -1921,11 +1921,11 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.02</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -2160,13 +2160,13 @@
         <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Shb Da Nang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Thanh Hoa</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,34 +2405,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2546,72 +2546,72 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Cong An Nhan Dan</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,31 +2659,31 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -2800,72 +2800,72 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Becamex Binh Duong</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.25</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>2.28</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.44</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.6</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="BO10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BT10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5</v>
-      </c>
       <c r="BU10" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -3129,33 +3129,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3170,19 +3170,19 @@
         <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -3383,17 +3383,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3424,19 +3424,19 @@
         <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
         <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="J13" t="n">
-        <v>1.06</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.22</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.02</v>
       </c>
-      <c r="N14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.15</v>
-      </c>
       <c r="W14" t="n">
-        <v>2.92</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.32</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.81</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>1.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>1.23</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>1.06</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>1.32</v>
       </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>1.34</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="H18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK18" t="n">
         <v>4.8</v>
       </c>
-      <c r="I18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA18" t="n">
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN18" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD18" t="n">
+      <c r="BO18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0</v>
-      </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>1.54</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
         <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="AB19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>400</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>400</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP19" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="AS19" t="n">
         <v>11.5</v>
       </c>
       <c r="AT19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB19" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BC19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG19" t="n">
         <v>10</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE19" t="n">
+      <c r="BH19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BV19" t="n">
         <v>11.5</v>
       </c>
-      <c r="BF19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>38</v>
-      </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BX19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,192 +5415,192 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>1.34</v>
       </c>
       <c r="O20" t="n">
         <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,13 +5612,13 @@
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
@@ -5630,7 +5630,7 @@
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5645,21 +5645,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>1.93</v>
       </c>
       <c r="H21" t="n">
-        <v>1.52</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,244 +5923,1260 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>2.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-06 07:38:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2</v>
+      </c>
+      <c r="X23" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-06 07:38:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Uruguay Montevideo FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>60</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-06 07:38:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.28</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W25" t="n">
         <v>1.82</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X25" t="n">
         <v>13</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y25" t="n">
         <v>15</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z25" t="n">
         <v>36</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA25" t="n">
         <v>120</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AB25" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AC25" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AD25" t="n">
         <v>22</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE25" t="n">
         <v>80</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AF25" t="n">
         <v>15</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AG25" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AH25" t="n">
         <v>26</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AI25" t="n">
         <v>95</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AJ25" t="n">
         <v>34</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AK25" t="n">
         <v>32</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AL25" t="n">
         <v>60</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AM25" t="n">
         <v>180</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AN25" t="n">
         <v>27</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AO25" t="n">
         <v>110</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AP25" t="n">
         <v>8</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AQ25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-06 07:38:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO26" t="n">
         <v>3.55</v>
       </c>
-      <c r="AR22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
+      <c r="BP26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT26" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-06-06 05:26:12</t>
+      <c r="BU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>27</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,37 +860,37 @@
         <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H2" t="n">
         <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -899,188 +899,188 @@
         <v>4.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.51</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.51</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.51</v>
+        <v>3.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
         <v>4.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
         <v>2.5</v>
@@ -1282,13 +1282,13 @@
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
@@ -1300,41 +1300,41 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
         <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.32</v>
@@ -1395,25 +1395,25 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
         <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
         <v>1.37</v>
@@ -1530,7 +1530,7 @@
         <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
         <v>4.8</v>
@@ -1634,7 +1634,7 @@
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1784,7 +1784,7 @@
         <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.06</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>1.17</v>
+        <v>2.32</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>2.54</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.31</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shb Da Nang</t>
+          <t>Ninh Binh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thanh Hoa</t>
+          <t>Hong Linh Ha Tinh</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -2626,28 +2626,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>Shb Da Nang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cong An Nhan Dan</t>
+          <t>Thanh Hoa</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,16 +2659,16 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.28</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="R9" t="n">
         <v>1.16</v>
@@ -2677,16 +2677,16 @@
         <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -2880,127 +2880,127 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Becamex Binh Duong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.65</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z10" t="n">
         <v>21</v>
       </c>
-      <c r="Y10" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>50</v>
-      </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
         <v>80</v>
       </c>
-      <c r="AF10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
       <c r="AN10" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
         <v>1.01</v>
@@ -3009,58 +3009,58 @@
         <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
         <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
         <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,28 +3069,28 @@
         <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3105,21 +3105,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,108 +3129,108 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>PVF-Cong An Nhan Dan</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="J11" t="n">
-        <v>1.06</v>
+        <v>5.7</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>2.54</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
@@ -3248,13 +3248,13 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AP11" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
         <v>1.01</v>
@@ -3275,28 +3275,28 @@
         <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3305,75 +3305,75 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Cong An Nhan Dan</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>1.06</v>
+        <v>2.08</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>1.23</v>
+        <v>2.54</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Becamex Binh Duong</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.6</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.43</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W13" t="n">
         <v>2.32</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF13" t="n">
         <v>13</v>
       </c>
-      <c r="Y13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="n">
         <v>40</v>
       </c>
-      <c r="AB13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AM13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN13" t="n">
+      <c r="CA13" t="n">
         <v>6.8</v>
       </c>
-      <c r="BO13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>11</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Ha Noi FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,34 +3929,34 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.16</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4070,65 +4070,65 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.06</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.32</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>1.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="J16" t="n">
-        <v>1.06</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.32</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2</v>
+        <v>1.06</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.02</v>
       </c>
-      <c r="N17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="W17" t="n">
-        <v>2.92</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>1.06</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>1.32</v>
       </c>
       <c r="O18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.32</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.86</v>
-      </c>
       <c r="Q18" t="n">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>1.06</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>1.32</v>
       </c>
       <c r="O19" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,33 +5415,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="G20" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>1.15</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="G21" t="n">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.08</v>
+        <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC21" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AE21" t="n">
         <v>90</v>
       </c>
       <c r="AF21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="BU21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>0</v>
-      </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>1.24</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.95</v>
       </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT23" t="n">
         <v>5.3</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="BU23" t="n">
         <v>4</v>
       </c>
-      <c r="AX23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>6</v>
-      </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="G24" t="n">
-        <v>2.78</v>
+        <v>10.5</v>
       </c>
       <c r="H24" t="n">
-        <v>3.15</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="J24" t="n">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.3</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.84</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>400</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>400</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ24" t="n">
+      <c r="BN24" t="n">
         <v>12</v>
       </c>
-      <c r="BK24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BO24" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="BP24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BR24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="BV24" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>2.06</v>
+        <v>5.7</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="G25" t="n">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="K25" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.28</v>
+        <v>1.21</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.97</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,81 +6939,81 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="G26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.1</v>
       </c>
-      <c r="H26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.26</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="U26" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA26" t="n">
         <v>160</v>
@@ -7022,161 +7022,1939 @@
         <v>8</v>
       </c>
       <c r="AC26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AZ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chilean Segunda Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Real San Joaquin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Concon National FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chilean Segunda Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Santiago Morning</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CD General Velasquez</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
         <v>24</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AS29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Uruguay Montevideo FC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>60</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE33" t="n">
         <v>100</v>
       </c>
-      <c r="AF26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AF33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN33" t="n">
         <v>27</v>
       </c>
-      <c r="AI26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ26" t="n">
+      <c r="AO33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>12</v>
       </c>
-      <c r="BK26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN26" t="n">
+      <c r="BK33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN33" t="n">
         <v>4.6</v>
       </c>
-      <c r="BO26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>27</v>
-      </c>
-      <c r="BT26" t="n">
+      <c r="BO33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BT33" t="n">
         <v>8.4</v>
       </c>
-      <c r="BU26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV26" t="n">
+      <c r="BU33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV33" t="n">
         <v>55</v>
       </c>
-      <c r="BW26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA26" t="n">
-        <v>27</v>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-06-06 07:38:48</t>
+      <c r="BW33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>42</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -860,34 +860,34 @@
         <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H2" t="n">
         <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
         <v>2.52</v>
@@ -899,22 +899,22 @@
         <v>4.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W2" t="n">
         <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>970</v>
@@ -923,7 +923,7 @@
         <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -932,7 +932,7 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>24</v>
@@ -947,7 +947,7 @@
         <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
         <v>60</v>
@@ -962,7 +962,7 @@
         <v>80</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
         <v>6.6</v>
@@ -971,10 +971,10 @@
         <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -983,76 +983,76 @@
         <v>5.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
         <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BH2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
         <v>5</v>
       </c>
-      <c r="BF2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="BN2" t="n">
         <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="BT2" t="n">
         <v>5.8</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
@@ -1123,7 +1123,7 @@
         <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -1141,7 +1141,7 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
         <v>2.14</v>
@@ -1162,19 +1162,19 @@
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB3" t="n">
         <v>9.4</v>
@@ -1183,10 +1183,10 @@
         <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1198,7 +1198,7 @@
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1219,19 +1219,19 @@
         <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
         <v>16.5</v>
@@ -1261,16 +1261,16 @@
         <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1530,7 +1530,7 @@
         <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
         <v>5.5</v>
@@ -1634,7 +1634,7 @@
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1652,7 +1652,7 @@
         <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
@@ -1670,7 +1670,7 @@
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1685,7 +1685,7 @@
         <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9.4</v>
@@ -1694,7 +1694,7 @@
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
         <v>13.5</v>
@@ -1733,10 +1733,10 @@
         <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1748,7 +1748,7 @@
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
@@ -1760,25 +1760,25 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1873,34 +1873,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.42</v>
@@ -1909,130 +1909,130 @@
         <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -2127,166 +2127,166 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I7" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="J7" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G8" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
         <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
         <v>2.38</v>
@@ -2411,7 +2411,7 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
         <v>1.47</v>
@@ -2423,16 +2423,16 @@
         <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -2638,34 +2638,34 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
         <v>1.23</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="I10" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="J10" t="n">
         <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -2913,49 +2913,49 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB10" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
         <v>970</v>
@@ -2964,10 +2964,10 @@
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2976,143 +2976,143 @@
         <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
         <v>970</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -3143,61 +3143,61 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="I11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="J11" t="n">
         <v>5.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
         <v>8.199999999999999</v>
@@ -3209,25 +3209,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AC11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>18.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AG11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
@@ -3236,137 +3236,137 @@
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AP11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BT11" t="n">
         <v>3.85</v>
       </c>
-      <c r="BI11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -3400,172 +3400,172 @@
         <v>2.86</v>
       </c>
       <c r="G12" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI12" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK12" t="n">
         <v>1.04</v>
@@ -3577,50 +3577,50 @@
         <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO12" t="n">
         <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS12" t="n">
         <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU12" t="n">
         <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW12" t="n">
         <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY12" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA12" t="n">
         <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.8</v>
@@ -3675,34 +3675,34 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3729,10 +3729,10 @@
         <v>95</v>
       </c>
       <c r="AF13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -3741,7 +3741,7 @@
         <v>90</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK13" t="n">
         <v>21</v>
@@ -3753,70 +3753,70 @@
         <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO13" t="n">
         <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC13" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF13" t="n">
         <v>3.1</v>
       </c>
-      <c r="AV13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3</v>
-      </c>
       <c r="BG13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="n">
         <v>3.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
@@ -3828,13 +3828,13 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP13" t="n">
         <v>11</v>
@@ -3849,32 +3849,32 @@
         <v>7.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BZ13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA13" t="n">
         <v>6.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G14" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="I14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.02</v>
       </c>
-      <c r="K14" t="n">
-        <v>950</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4070,65 +4070,65 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
         <v>3.3</v>
@@ -4168,7 +4168,7 @@
         <v>2.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
@@ -4186,13 +4186,13 @@
         <v>5.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.58</v>
@@ -4201,10 +4201,10 @@
         <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
         <v>1.62</v>
@@ -4246,7 +4246,7 @@
         <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ15" t="n">
         <v>60</v>
@@ -4255,7 +4255,7 @@
         <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
         <v>70</v>
@@ -4267,58 +4267,58 @@
         <v>13.5</v>
       </c>
       <c r="AP15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR15" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AS15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX15" t="n">
         <v>4</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AY15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>3.65</v>
       </c>
-      <c r="AU15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BA15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC15" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.95</v>
       </c>
       <c r="BD15" t="n">
         <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BH15" t="n">
         <v>4.5</v>
@@ -4330,13 +4330,13 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
         <v>6.8</v>
@@ -4348,13 +4348,13 @@
         <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
         <v>6</v>
@@ -4363,26 +4363,26 @@
         <v>4.4</v>
       </c>
       <c r="BV15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>16.5</v>
       </c>
-      <c r="BW15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>17.5</v>
-      </c>
       <c r="CA15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
         <v>2.28</v>
@@ -4425,13 +4425,13 @@
         <v>2.44</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
@@ -4578,7 +4578,7 @@
         <v>2.9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4697,28 +4697,28 @@
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>1.09</v>
       </c>
       <c r="G20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5468,7 +5468,7 @@
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K21" t="n">
         <v>6.4</v>
-      </c>
-      <c r="I21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>1.19</v>
@@ -5707,10 +5707,10 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P21" t="n">
         <v>3.05</v>
@@ -5722,19 +5722,19 @@
         <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U21" t="n">
         <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -5773,10 +5773,10 @@
         <v>75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL21" t="n">
         <v>30</v>
@@ -5785,22 +5785,22 @@
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO21" t="n">
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -5812,19 +5812,19 @@
         <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -5836,13 +5836,13 @@
         <v>18</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF21" t="n">
         <v>3.65</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
         <v>5.4</v>
@@ -5854,13 +5854,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.7</v>
@@ -5872,16 +5872,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU21" t="n">
         <v>5.8</v>
@@ -5890,23 +5890,23 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ21" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,7 +5961,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
         <v>1.01</v>
@@ -5970,7 +5970,7 @@
         <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.12</v>
@@ -5985,10 +5985,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -6191,25 +6191,25 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.4</v>
       </c>
-      <c r="G23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -6221,7 +6221,7 @@
         <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
         <v>1.95</v>
@@ -6269,19 +6269,19 @@
         <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="n">
         <v>55</v>
@@ -6293,22 +6293,22 @@
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AT23" t="n">
         <v>10.5</v>
@@ -6317,13 +6317,13 @@
         <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY23" t="n">
         <v>11.5</v>
@@ -6332,25 +6332,25 @@
         <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC23" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
         <v>4.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH23" t="n">
         <v>3.5</v>
@@ -6362,16 +6362,16 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO23" t="n">
         <v>5.4</v>
@@ -6380,13 +6380,13 @@
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT23" t="n">
         <v>5.3</v>
@@ -6395,26 +6395,26 @@
         <v>4</v>
       </c>
       <c r="BV23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
         <v>7</v>
       </c>
-      <c r="BZ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1.74</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6747,10 +6747,10 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G26" t="n">
         <v>1.95</v>
@@ -6962,13 +6962,13 @@
         <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J26" t="n">
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
         <v>1.92</v>
       </c>
       <c r="U26" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -7079,7 +7079,7 @@
         <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AW26" t="n">
         <v>7.6</v>
@@ -7088,7 +7088,7 @@
         <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -7231,13 +7231,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.29</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" t="n">
         <v>1.84</v>
@@ -7249,10 +7249,10 @@
         <v>2.46</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.01</v>
@@ -7500,13 +7500,13 @@
         <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -7742,10 +7742,10 @@
         <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
         <v>2.26</v>
@@ -7781,13 +7781,13 @@
         <v>85</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC29" t="n">
         <v>7.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE29" t="n">
         <v>60</v>
@@ -7823,19 +7823,19 @@
         <v>70</v>
       </c>
       <c r="AP29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
         <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
@@ -7868,10 +7868,10 @@
         <v>40</v>
       </c>
       <c r="BE29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG29" t="n">
         <v>50</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
         <v>1.52</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T30" t="n">
         <v>1.61</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
         <v>1.16</v>
       </c>
       <c r="S31" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="T31" t="n">
         <v>2.2</v>
@@ -8388,7 +8388,7 @@
         <v>2.58</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="BJ31" t="n">
         <v>12</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -8731,139 +8731,139 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
         <v>5.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K33" t="n">
         <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O33" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P33" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W33" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA33" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC33" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE33" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG33" t="n">
         <v>13</v>
       </c>
       <c r="AH33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>28</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>29</v>
       </c>
       <c r="AK33" t="n">
         <v>32</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM33" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN33" t="n">
         <v>27</v>
       </c>
       <c r="AO33" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR33" t="n">
         <v>4.9</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AV33" t="n">
         <v>4.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY33" t="n">
         <v>3.9</v>
@@ -8890,71 +8890,71 @@
         <v>4.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="BN33" t="n">
         <v>4.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP33" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR33" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
         <v>2.18</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>2.22</v>
       </c>
       <c r="BZ33" t="n">
         <v>42</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,7 +890,7 @@
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -908,7 +908,7 @@
         <v>1.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>9.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
         <v>2.14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
         <v>2.18</v>
@@ -1398,7 +1398,7 @@
         <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1649,10 +1649,10 @@
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
@@ -1667,10 +1667,10 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1688,7 +1688,7 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1697,7 +1697,7 @@
         <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1709,7 +1709,7 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
         <v>24</v>
@@ -1730,13 +1730,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1745,13 +1745,13 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AY5" t="n">
         <v>8.4</v>
@@ -1760,31 +1760,31 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="n">
-        <v>13</v>
-      </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Ha Noi FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="G6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,142 +1897,142 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.15</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>1.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Vietnamese V-League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Becamex Binh Duong</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>1.71</v>
       </c>
       <c r="H7" t="n">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL7" t="n">
         <v>40</v>
       </c>
-      <c r="AL7" t="n">
-        <v>48</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.18</v>
+        <v>3.95</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.02</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AV7" t="n">
         <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="AY7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BE7" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ninh Binh</t>
+          <t>Viettel FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hong Linh Ha Tinh</t>
+          <t>Cong An Nhan Dan</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.47</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>28</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="X8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP8" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" t="n">
-        <v>12</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shb Da Nang</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thanh Hoa</t>
+          <t>PVF-Cong An Nhan Dan</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>1.54</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="J9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V9" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG9" t="n">
         <v>950</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
         <v>4.4</v>
@@ -2913,16 +2913,16 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
         <v>1.5</v>
@@ -3003,13 +3003,13 @@
         <v>3.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AS10" t="n">
         <v>3.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AU10" t="n">
         <v>3.1</v>
@@ -3024,7 +3024,7 @@
         <v>3.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ10" t="n">
         <v>3.5</v>
@@ -3036,10 +3036,10 @@
         <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shb Da Nang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PVF-Cong An Nhan Dan</t>
+          <t>Thanh Hoa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>1.54</v>
       </c>
       <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S11" t="n">
         <v>1.28</v>
       </c>
-      <c r="I11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.88</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>2.84</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -3388,187 +3388,187 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Viettel FC</t>
+          <t>Ninh Binh</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cong An Nhan Dan</t>
+          <t>Hong Linh Ha Tinh</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X12" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD12" t="n">
         <v>2.86</v>
       </c>
-      <c r="G12" t="n">
+      <c r="BE12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.1</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BG12" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,57 +3577,57 @@
         <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BR12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
         <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BZ12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vietnamese V-League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,202 +3642,202 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Becamex Binh Duong</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS13" t="n">
         <v>4.9</v>
       </c>
-      <c r="I13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BO13" t="n">
         <v>3.8</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BP13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
         <v>5.5</v>
@@ -3846,42 +3846,42 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.76</v>
+        <v>1.81</v>
       </c>
       <c r="BZ13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vietnamese V-League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,187 +3896,187 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ha Noi FC</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="AX14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BA14" t="n">
         <v>2.04</v>
       </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="BB14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BC14" t="n">
         <v>2.04</v>
       </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,13 +4088,13 @@
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4106,19 +4106,19 @@
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -4168,10 +4168,10 @@
         <v>2.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>4.4</v>
@@ -4180,7 +4180,7 @@
         <v>1.24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
         <v>5.2</v>
@@ -4189,7 +4189,7 @@
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
         <v>1.5</v>
@@ -4207,10 +4207,10 @@
         <v>2.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
         <v>29</v>
@@ -4255,7 +4255,7 @@
         <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
         <v>70</v>
@@ -4267,58 +4267,58 @@
         <v>13.5</v>
       </c>
       <c r="AP15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS15" t="n">
         <v>4</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AT15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU15" t="n">
         <v>3.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AY15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.65</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
         <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BH15" t="n">
         <v>4.5</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="H16" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="I16" t="n">
-        <v>2.44</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X16" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP16" t="n">
         <v>3.6</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X16" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="AS16" t="n">
-        <v>28</v>
+        <v>3.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>3.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.6</v>
+        <v>3.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>44</v>
+        <v>3.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BC16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.6</v>
+        <v>1.05</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>11</v>
+        <v>1.23</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>11</v>
+        <v>1.09</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU17" t="n">
         <v>3.85</v>
       </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>110</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.06</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4942,7 +4942,7 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
         <v>1.32</v>
@@ -4957,10 +4957,10 @@
         <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -5175,230 +5175,230 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.06</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.32</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>1.32</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -5429,230 +5429,230 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>5.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>1.16</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>5.3</v>
       </c>
       <c r="K21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.19</v>
@@ -5719,10 +5719,10 @@
         <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>1.61</v>
@@ -5845,75 +5845,75 @@
         <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI21" t="n">
         <v>4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.7</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT21" t="n">
         <v>11</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>9.6</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CA21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>1.47</v>
+        <v>2.96</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -5985,10 +5985,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6045,52 +6045,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -6099,10 +6099,10 @@
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,246 +6436,246 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP24" t="n">
         <v>10.5</v>
       </c>
-      <c r="H24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="AQ24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS24" t="n">
         <v>4.4</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>400</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>210</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>400</v>
-      </c>
-      <c r="AO24" t="n">
+      <c r="AT24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG24" t="n">
         <v>14</v>
       </c>
-      <c r="AP24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU24" t="n">
+      <c r="BH24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN24" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BO24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
         <v>7</v>
       </c>
-      <c r="AY24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,66 +6685,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
@@ -6753,183 +6753,183 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,246 +6944,246 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T26" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,239 +7198,239 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Real San Joaquin</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Concon National FC</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="H27" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Real San Joaquin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD General Velasquez</t>
+          <t>Concon National FC</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P28" t="n">
         <v>1.25</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q28" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="R28" t="n">
         <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7569,52 +7569,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -7626,72 +7626,72 @@
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,246 +7706,246 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>CD General Velasquez</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>1.05</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>1.38</v>
       </c>
       <c r="T29" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,251 +7955,251 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="H30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
         <v>4.3</v>
       </c>
-      <c r="O30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.3</v>
-      </c>
       <c r="T30" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="X30" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AE30" t="n">
         <v>60</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB30" t="n">
         <v>25</v>
       </c>
-      <c r="AK30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS30" t="n">
+      <c r="BC30" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO30" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF30" t="n">
+      <c r="BP30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ30" t="n">
         <v>6.6</v>
       </c>
-      <c r="BG30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU30" t="n">
         <v>6</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,251 +8209,251 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="G31" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="I31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR31" t="n">
         <v>3.95</v>
       </c>
-      <c r="J31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP31" t="n">
+      <c r="AS31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI31" t="n">
         <v>3.25</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BJ31" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
         <v>5.4</v>
       </c>
-      <c r="BO31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>2</v>
-      </c>
       <c r="BR31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV31" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,189 +8463,189 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="P32" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="T32" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W32" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="X32" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE32" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI32" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AK32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AL32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN32" t="n">
         <v>60</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>27</v>
       </c>
       <c r="AO32" t="n">
         <v>110</v>
       </c>
       <c r="AP32" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="AV32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY32" t="n">
         <v>3.95</v>
       </c>
-      <c r="AW32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH32" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="BJ32" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="BK32" t="n">
         <v>6.4</v>
@@ -8654,60 +8654,60 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="BN32" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BR32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,244 +8717,498 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H33" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="U33" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="V33" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="W33" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="X33" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z33" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AB33" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE33" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AF33" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI33" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AK33" t="n">
         <v>32</v>
       </c>
       <c r="AL33" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
         <v>27</v>
       </c>
       <c r="AO33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-06-06 14:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA34" t="n">
         <v>180</v>
       </c>
-      <c r="AP33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR33" t="n">
+      <c r="AB34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ33" t="n">
+      <c r="AX34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN34" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC33" t="n">
+      <c r="BO34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU34" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR33" t="n">
+      <c r="BV34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BZ34" t="n">
         <v>42</v>
       </c>
-      <c r="BS33" t="n">
+      <c r="CA34" t="n">
         <v>2.14</v>
       </c>
-      <c r="BT33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>42</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>2026-06-06 12:03:22</t>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -860,7 +860,7 @@
         <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
         <v>2.52</v>
@@ -908,7 +908,7 @@
         <v>1.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>9.6</v>
@@ -1019,16 +1019,16 @@
         <v>4.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,41 +1046,41 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.04</v>
+        <v>1.51</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.04</v>
+        <v>1.51</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
@@ -1129,7 +1129,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1150,7 +1150,7 @@
         <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
         <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
@@ -1395,19 +1395,19 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
         <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
         <v>2.22</v>
@@ -1416,31 +1416,31 @@
         <v>1.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
         <v>28</v>
@@ -1449,7 +1449,7 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>40</v>
@@ -1458,7 +1458,7 @@
         <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
         <v>50</v>
@@ -1470,7 +1470,7 @@
         <v>38</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>12.5</v>
@@ -1482,7 +1482,7 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
@@ -1494,10 +1494,10 @@
         <v>8.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1506,25 +1506,25 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>5.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1643,19 +1643,19 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
         <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
         <v>3.35</v>
@@ -1664,7 +1664,7 @@
         <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.21</v>
@@ -1685,13 +1685,13 @@
         <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>90</v>
@@ -1712,7 +1712,7 @@
         <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>38</v>
@@ -1730,13 +1730,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1745,13 +1745,13 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
         <v>8.4</v>
@@ -1760,25 +1760,25 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
         <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
         <v>1.15</v>
@@ -1906,7 +1906,7 @@
         <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
         <v>1.74</v>
@@ -2244,16 +2244,16 @@
         <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU7" t="n">
         <v>3.4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
         <v>4.5</v>
@@ -2262,13 +2262,13 @@
         <v>3.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
         <v>3.85</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>2.76</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.85</v>
@@ -2402,7 +2402,7 @@
         <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
         <v>1.1</v>
@@ -2411,16 +2411,16 @@
         <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
@@ -2432,7 +2432,7 @@
         <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
@@ -2546,10 +2546,10 @@
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
         <v>5.1</v>
@@ -2558,13 +2558,13 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP8" t="n">
         <v>22</v>
@@ -2576,19 +2576,19 @@
         <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="BT8" t="n">
         <v>5.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV8" t="n">
         <v>19</v>
       </c>
       <c r="BW8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX8" t="n">
         <v>30</v>
@@ -2600,11 +2600,11 @@
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
         <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I9" t="n">
         <v>1.32</v>
@@ -2650,7 +2650,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2665,10 +2665,10 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2680,10 +2680,10 @@
         <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
@@ -2743,7 +2743,7 @@
         <v>5.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
         <v>3.65</v>
@@ -2752,22 +2752,22 @@
         <v>3.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
         <v>4.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
         <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
@@ -2776,7 +2776,7 @@
         <v>5.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
         <v>6.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>4.4</v>
@@ -2913,13 +2913,13 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
         <v>1.53</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="H12" t="n">
         <v>5.1</v>
@@ -3409,19 +3409,19 @@
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
@@ -3436,7 +3436,7 @@
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
         <v>1.72</v>
@@ -3448,7 +3448,7 @@
         <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
         <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
@@ -3684,7 +3684,7 @@
         <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.54</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
         <v>3.55</v>
@@ -3920,7 +3920,7 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.31</v>
@@ -3953,7 +3953,7 @@
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
         <v>1.39</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -4159,166 +4159,166 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.56</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI15" t="n">
         <v>27</v>
       </c>
-      <c r="AF15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="n">
         <v>4.5</v>
@@ -4330,31 +4330,31 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BO15" t="n">
         <v>4.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
         <v>6</v>
@@ -4363,26 +4363,26 @@
         <v>4.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BW15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY15" t="n">
         <v>6.4</v>
       </c>
-      <c r="BX15" t="n">
-        <v>24</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BZ15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="G16" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>2.82</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -4437,7 +4437,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
@@ -4446,13 +4446,13 @@
         <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.58</v>
@@ -4461,10 +4461,10 @@
         <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4473,10 +4473,10 @@
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AB16" t="n">
         <v>970</v>
@@ -4488,10 +4488,10 @@
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF16" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -4500,16 +4500,16 @@
         <v>970</v>
       </c>
       <c r="AI16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="n">
         <v>44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
@@ -4518,61 +4518,61 @@
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>3.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AT16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY16" t="n">
         <v>3.35</v>
       </c>
-      <c r="AU16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BB16" t="n">
         <v>3.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4590,53 +4590,53 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -4667,40 +4667,40 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H17" t="n">
         <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J17" t="n">
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P17" t="n">
         <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
@@ -4709,7 +4709,7 @@
         <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
         <v>1.87</v>
@@ -4718,13 +4718,13 @@
         <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
         <v>14</v>
@@ -4733,22 +4733,22 @@
         <v>34</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
         <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
@@ -4757,7 +4757,7 @@
         <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
         <v>50</v>
@@ -4772,7 +4772,7 @@
         <v>65</v>
       </c>
       <c r="AO17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP17" t="n">
         <v>8.199999999999999</v>
@@ -4781,22 +4781,22 @@
         <v>7.2</v>
       </c>
       <c r="AR17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>10</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AW17" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>16.5</v>
@@ -4814,25 +4814,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE17" t="n">
         <v>10.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG17" t="n">
         <v>21</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17" t="n">
         <v>11</v>
@@ -4847,7 +4847,7 @@
         <v>14.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO17" t="n">
         <v>5</v>
@@ -4865,16 +4865,16 @@
         <v>12</v>
       </c>
       <c r="BT17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -4945,22 +4945,22 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q18" t="n">
         <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -5175,70 +5175,70 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.75</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
         <v>1.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
         <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
         <v>970</v>
@@ -5250,7 +5250,7 @@
         <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
         <v>970</v>
@@ -5262,16 +5262,16 @@
         <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -5280,7 +5280,7 @@
         <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP19" t="n">
         <v>3.5</v>
@@ -5292,10 +5292,10 @@
         <v>3.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AU19" t="n">
         <v>3.05</v>
@@ -5304,19 +5304,19 @@
         <v>3.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>3.7</v>
@@ -5325,19 +5325,19 @@
         <v>3.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG19" t="n">
         <v>4</v>
       </c>
-      <c r="BF19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BH19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BI19" t="n">
         <v>2.96</v>
@@ -5346,37 +5346,37 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
@@ -5388,7 +5388,7 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -5462,7 +5462,7 @@
         <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R20" t="n">
         <v>1.6</v>
@@ -5477,16 +5477,16 @@
         <v>1.85</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
         <v>130</v>
@@ -5495,7 +5495,7 @@
         <v>460</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>16.5</v>
@@ -5525,7 +5525,7 @@
         <v>16.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
         <v>160</v>
@@ -5540,13 +5540,13 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
@@ -5555,10 +5555,10 @@
         <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
         <v>7</v>
@@ -5570,7 +5570,7 @@
         <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB20" t="n">
         <v>8.199999999999999</v>
@@ -5579,16 +5579,16 @@
         <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="n">
         <v>4.8</v>
@@ -5612,7 +5612,7 @@
         <v>4.1</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP20" t="n">
         <v>7.8</v>
@@ -5630,7 +5630,7 @@
         <v>14.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5648,11 +5648,11 @@
         <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>1.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H21" t="n">
         <v>6.6</v>
@@ -5725,13 +5725,13 @@
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U21" t="n">
         <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W21" t="n">
         <v>3</v>
@@ -5740,7 +5740,7 @@
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="Z21" t="n">
         <v>80</v>
@@ -5761,7 +5761,7 @@
         <v>90</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
@@ -5791,16 +5791,16 @@
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.3</v>
+        <v>26</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -5824,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -5839,10 +5839,10 @@
         <v>4.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH21" t="n">
         <v>5.3</v>
@@ -5875,7 +5875,7 @@
         <v>5.3</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS21" t="n">
         <v>7.8</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H22" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
         <v>4.1</v>
@@ -5952,7 +5952,7 @@
         <v>2.92</v>
       </c>
       <c r="K22" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,10 +5961,10 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
         <v>1.54</v>
@@ -5979,16 +5979,16 @@
         <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V22" t="n">
         <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6108,59 +6108,59 @@
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6230,7 +6230,7 @@
         <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I24" t="n">
         <v>2.38</v>
@@ -6460,16 +6460,16 @@
         <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.32</v>
@@ -6481,16 +6481,16 @@
         <v>1.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
         <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -6523,10 +6523,10 @@
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
@@ -6535,7 +6535,7 @@
         <v>46</v>
       </c>
       <c r="AJ24" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK24" t="n">
         <v>55</v>
@@ -6547,7 +6547,7 @@
         <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO24" t="n">
         <v>21</v>
@@ -6556,13 +6556,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
@@ -6571,13 +6571,13 @@
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW24" t="n">
         <v>18.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
         <v>11.5</v>
@@ -6586,22 +6586,22 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB24" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BC24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
         <v>14</v>
@@ -6610,19 +6610,19 @@
         <v>3.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6634,16 +6634,16 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU24" t="n">
         <v>4</v>
@@ -6652,23 +6652,23 @@
         <v>17</v>
       </c>
       <c r="BW24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>7.4</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H25" t="n">
         <v>1.54</v>
@@ -6714,13 +6714,13 @@
         <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
         <v>2.86</v>
@@ -6783,7 +6783,7 @@
         <v>950</v>
       </c>
       <c r="AH25" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI25" t="n">
         <v>60</v>
@@ -6840,7 +6840,7 @@
         <v>6.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="BB25" t="n">
         <v>7.6</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="G27" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7252,7 +7252,7 @@
         <v>1.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -7264,7 +7264,7 @@
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z27" t="n">
         <v>40</v>
@@ -7276,10 +7276,10 @@
         <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>90</v>
@@ -7297,7 +7297,7 @@
         <v>95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK27" t="n">
         <v>23</v>
@@ -7312,7 +7312,7 @@
         <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP27" t="n">
         <v>9.199999999999999</v>
@@ -7321,10 +7321,10 @@
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -7336,7 +7336,7 @@
         <v>16.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>8</v>
@@ -7345,10 +7345,10 @@
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -7357,16 +7357,16 @@
         <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -7461,91 +7461,91 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="J28" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
         <v>1.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="R28" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>1.31</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -7566,7 +7566,7 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -7715,46 +7715,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.72</v>
       </c>
       <c r="H29" t="n">
-        <v>1.02</v>
+        <v>2.98</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S29" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -7763,10 +7763,10 @@
         <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7877,13 +7877,13 @@
         <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK29" t="n">
         <v>1.04</v>
@@ -7895,25 +7895,25 @@
         <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO29" t="n">
         <v>1.04</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.04</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS29" t="n">
         <v>1.04</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU29" t="n">
         <v>1.04</v>
@@ -7931,14 +7931,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA29" t="n">
         <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>2.22</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I30" t="n">
         <v>4.1</v>
@@ -7996,22 +7996,22 @@
         <v>3.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U30" t="n">
         <v>1.95</v>
@@ -8020,7 +8020,7 @@
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
@@ -8035,7 +8035,7 @@
         <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC30" t="n">
         <v>7.6</v>
@@ -8053,7 +8053,7 @@
         <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>70</v>
@@ -8086,7 +8086,7 @@
         <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT30" t="n">
         <v>7.8</v>
@@ -8095,10 +8095,10 @@
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX30" t="n">
         <v>11</v>
@@ -8122,7 +8122,7 @@
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF30" t="n">
         <v>19</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -8331,58 +8331,58 @@
         <v>46</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.95</v>
+        <v>2.08</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AW31" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AY31" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BA31" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="BB31" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.85</v>
+        <v>2.44</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.1</v>
+        <v>2.14</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="BG31" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         <v>2.78</v>
       </c>
       <c r="H32" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I32" t="n">
         <v>3.95</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -8737,13 +8737,13 @@
         <v>2.22</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I33" t="n">
         <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
@@ -8779,7 +8779,7 @@
         <v>1.78</v>
       </c>
       <c r="V33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
         <v>1.82</v>
@@ -8800,7 +8800,7 @@
         <v>9.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD33" t="n">
         <v>22</v>
@@ -8842,7 +8842,7 @@
         <v>8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AR33" t="n">
         <v>21</v>
@@ -8857,31 +8857,31 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AY33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC33" t="n">
         <v>19</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE33" t="n">
         <v>4.6</v>
@@ -8890,7 +8890,7 @@
         <v>16</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="n">
         <v>3</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -8985,31 +8985,31 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>2.88</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
@@ -9018,13 +9018,13 @@
         <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="T34" t="n">
         <v>2.1</v>
@@ -9033,31 +9033,31 @@
         <v>1.72</v>
       </c>
       <c r="V34" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X34" t="n">
         <v>11</v>
       </c>
       <c r="Y34" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA34" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE34" t="n">
         <v>110</v>
@@ -9075,7 +9075,7 @@
         <v>130</v>
       </c>
       <c r="AJ34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK34" t="n">
         <v>32</v>
@@ -9087,128 +9087,128 @@
         <v>230</v>
       </c>
       <c r="AN34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO34" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AU34" t="n">
         <v>3.25</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BA34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD34" t="n">
         <v>5</v>
       </c>
-      <c r="BB34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BJ34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK34" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BN34" t="n">
         <v>4.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP34" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR34" t="n">
         <v>40</v>
       </c>
       <c r="BS34" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BT34" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW34" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BZ34" t="n">
         <v>42</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -860,7 +860,7 @@
         <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
         <v>2.52</v>
@@ -875,7 +875,7 @@
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -890,7 +890,7 @@
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -923,7 +923,7 @@
         <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -971,7 +971,7 @@
         <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
         <v>4.8</v>
@@ -983,16 +983,16 @@
         <v>5.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
         <v>4.4</v>
@@ -1019,10 +1019,10 @@
         <v>4.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1055,16 +1055,16 @@
         <v>1.51</v>
       </c>
       <c r="BT2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.46</v>
+        <v>3.05</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
         <v>2.14</v>
@@ -1162,7 +1162,7 @@
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
@@ -1177,7 +1177,7 @@
         <v>140</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>9.6</v>
@@ -1186,37 +1186,37 @@
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>380</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AP3" t="n">
         <v>8.800000000000001</v>
@@ -1225,22 +1225,22 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1249,34 +1249,34 @@
         <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1291,16 +1291,16 @@
         <v>11.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1309,16 +1309,16 @@
         <v>9</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.32</v>
@@ -1389,7 +1389,7 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
@@ -1401,7 +1401,7 @@
         <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
         <v>3.05</v>
@@ -1410,16 +1410,16 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1428,49 +1428,49 @@
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="AK4" t="n">
         <v>44</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO4" t="n">
         <v>38</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>12.5</v>
@@ -1482,7 +1482,7 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
@@ -1494,10 +1494,10 @@
         <v>8.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1506,34 +1506,34 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF4" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="n">
         <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK4" t="n">
         <v>5.4</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
         <v>6.8</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="BT4" t="n">
         <v>5.4</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1643,43 +1643,43 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
         <v>160</v>
@@ -1691,7 +1691,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>90</v>
@@ -1718,25 +1718,25 @@
         <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
         <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="AP5" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1745,10 +1745,10 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>9.6</v>
@@ -1760,25 +1760,25 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
         <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
         <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="H6" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,22 +1897,22 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
         <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,58 +1981,58 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -2169,16 +2169,16 @@
         <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
         <v>22</v>
@@ -2196,13 +2196,13 @@
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="AF7" t="n">
         <v>12.5</v>
@@ -2211,7 +2211,7 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>90</v>
@@ -2226,73 +2226,73 @@
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AR7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BA7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF7" t="n">
         <v>3.4</v>
       </c>
-      <c r="AV7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2304,13 +2304,13 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP7" t="n">
         <v>11</v>
@@ -2325,32 +2325,32 @@
         <v>7.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA7" t="n">
         <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
         <v>2.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.3</v>
@@ -2420,7 +2420,7 @@
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
@@ -2432,121 +2432,121 @@
         <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
         <v>22</v>
       </c>
-      <c r="AA8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.17</v>
+        <v>9.4</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H9" t="n">
         <v>1.26</v>
@@ -2650,7 +2650,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2668,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2680,10 +2680,10 @@
         <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
@@ -2701,7 +2701,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC9" t="n">
         <v>16.5</v>
@@ -2740,31 +2740,31 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" t="n">
         <v>5.9</v>
       </c>
-      <c r="AP9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AU9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV9" t="n">
         <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
@@ -2773,28 +2773,28 @@
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA9" t="n">
         <v>6</v>
       </c>
       <c r="BB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
         <v>4.4</v>
@@ -2901,7 +2901,7 @@
         <v>2.26</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
         <v>4.6</v>
@@ -2913,7 +2913,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2922,7 +2922,7 @@
         <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
         <v>1.5</v>
@@ -2952,40 +2952,40 @@
         <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>80</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AM10" t="n">
         <v>80</v>
@@ -2997,58 +2997,58 @@
         <v>970</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>3.35</v>
       </c>
-      <c r="AR10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BF10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G11" t="n">
         <v>1.54</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,19 +3167,19 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q11" t="n">
         <v>1.23</v>
       </c>
       <c r="R11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
         <v>1.28</v>
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
         <v>2.84</v>
@@ -3245,64 +3245,64 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
@@ -3421,13 +3421,13 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
         <v>1.55</v>
@@ -3445,10 +3445,10 @@
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3505,58 +3505,58 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.82</v>
+        <v>4.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="AW12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BF12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG12" t="n">
         <v>3.1</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
         <v>1.86</v>
@@ -3681,7 +3681,7 @@
         <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
         <v>1.6</v>
@@ -3720,7 +3720,7 @@
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
@@ -3735,13 +3735,13 @@
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
         <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
         <v>970</v>
@@ -3753,22 +3753,22 @@
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AO13" t="n">
-        <v>50</v>
+        <v>310</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3777,40 +3777,40 @@
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="n">
         <v>4.4</v>
@@ -3834,7 +3834,7 @@
         <v>18.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
         <v>3.55</v>
@@ -3920,7 +3920,7 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.31</v>
@@ -3935,7 +3935,7 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
         <v>1.75</v>
@@ -3950,10 +3950,10 @@
         <v>1.63</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
         <v>1.39</v>
@@ -3974,7 +3974,7 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
@@ -4013,58 +4013,58 @@
         <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AT14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV14" t="n">
         <v>4.4</v>
       </c>
-      <c r="AU14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="AX14" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="BH14" t="n">
         <v>8</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
@@ -4183,34 +4183,34 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
@@ -4243,13 +4243,13 @@
         <v>20</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>27</v>
       </c>
       <c r="AJ15" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="AK15" t="n">
         <v>40</v>
@@ -4258,7 +4258,7 @@
         <v>42</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN15" t="n">
         <v>27</v>
@@ -4267,61 +4267,61 @@
         <v>9.4</v>
       </c>
       <c r="AP15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT15" t="n">
+      <c r="AW15" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AX15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
         <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BI15" t="n">
         <v>3.35</v>
@@ -4330,31 +4330,31 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO15" t="n">
         <v>4.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
         <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT15" t="n">
         <v>6</v>
@@ -4366,23 +4366,23 @@
         <v>13.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX15" t="n">
         <v>22</v>
       </c>
       <c r="BY15" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -4419,16 +4419,16 @@
         <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -4443,22 +4443,22 @@
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
         <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
         <v>1.57</v>
@@ -4473,106 +4473,106 @@
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AA16" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK16" t="n">
         <v>55</v>
       </c>
-      <c r="AK16" t="n">
-        <v>36</v>
-      </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF16" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4584,13 +4584,13 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4608,7 +4608,7 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
@@ -4620,7 +4620,7 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4632,11 +4632,11 @@
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G17" t="n">
         <v>3.55</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I17" t="n">
         <v>2.46</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.65</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -4694,16 +4694,16 @@
         <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
         <v>2.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
         <v>4.7</v>
@@ -4730,7 +4730,7 @@
         <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>10</v>
@@ -4745,37 +4745,37 @@
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ17" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AO17" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
         <v>7.2</v>
@@ -4796,7 +4796,7 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX17" t="n">
         <v>16.5</v>
@@ -4832,7 +4832,7 @@
         <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="BJ17" t="n">
         <v>11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -4957,7 +4957,7 @@
         <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
         <v>1.23</v>
@@ -4969,10 +4969,10 @@
         <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -5175,230 +5175,230 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
         <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
         <v>3.7</v>
       </c>
-      <c r="BC19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.35</v>
+        <v>5.8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.36</v>
+        <v>5.9</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.19</v>
+        <v>5.9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.31</v>
       </c>
       <c r="G20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
         <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5600,7 +5600,7 @@
         <v>12.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -5686,16 +5686,16 @@
         <v>1.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I21" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K21" t="n">
         <v>6.2</v>
@@ -5713,16 +5713,16 @@
         <v>1.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
         <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T21" t="n">
         <v>1.62</v>
@@ -5731,43 +5731,43 @@
         <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Z21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA21" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="n">
         <v>17</v>
       </c>
-      <c r="AC21" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AD21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE21" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>75</v>
@@ -5779,52 +5779,52 @@
         <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO21" t="n">
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>26</v>
+        <v>4.1</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU21" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>10</v>
       </c>
       <c r="AV21" t="n">
         <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -5833,25 +5833,25 @@
         <v>10</v>
       </c>
       <c r="BD21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI21" t="n">
         <v>4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
         <v>5.6</v>
@@ -5860,25 +5860,25 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN21" t="n">
         <v>4.7</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR21" t="n">
         <v>18</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT21" t="n">
         <v>11</v>
@@ -5890,7 +5890,7 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
@@ -5902,11 +5902,11 @@
         <v>9.6</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
         <v>2.92</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5979,7 +5979,7 @@
         <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U22" t="n">
         <v>1.75</v>
@@ -6000,7 +6000,7 @@
         <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
         <v>1000</v>
@@ -6027,7 +6027,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -6197,13 +6197,13 @@
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O23" t="n">
         <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q23" t="n">
         <v>1.01</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -6463,13 +6463,13 @@
         <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>1.32</v>
@@ -6499,7 +6499,7 @@
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
         <v>11.5</v>
@@ -6556,7 +6556,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR24" t="n">
         <v>10.5</v>
@@ -6571,7 +6571,7 @@
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
         <v>18.5</v>
@@ -6586,7 +6586,7 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB24" t="n">
         <v>4.6</v>
@@ -6595,10 +6595,10 @@
         <v>4.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF24" t="n">
         <v>4.5</v>
@@ -6610,7 +6610,7 @@
         <v>3.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ24" t="n">
         <v>10</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G25" t="n">
         <v>9.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I25" t="n">
         <v>1.65</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
         <v>4.2</v>
@@ -6732,16 +6732,16 @@
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.28</v>
       </c>
       <c r="U25" t="n">
         <v>1.63</v>
@@ -6768,13 +6768,13 @@
         <v>950</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
         <v>75</v>
@@ -6786,28 +6786,28 @@
         <v>950</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ25" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="AK25" t="n">
+        <v>220</v>
+      </c>
+      <c r="AL25" t="n">
         <v>210</v>
       </c>
-      <c r="AL25" t="n">
-        <v>200</v>
-      </c>
       <c r="AM25" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN25" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
         <v>5.2</v>
@@ -6831,31 +6831,31 @@
         <v>16</v>
       </c>
       <c r="AX25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC25" t="n">
         <v>7</v>
       </c>
-      <c r="AY25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD25" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
         <v>13.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6900,7 +6900,7 @@
         <v>3.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BV25" t="n">
         <v>11.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G27" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
         <v>2.1</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -7461,178 +7461,178 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G28" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H28" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="I28" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J28" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>1.64</v>
       </c>
       <c r="W28" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7644,31 +7644,31 @@
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -7715,230 +7715,230 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="G29" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H29" t="n">
-        <v>2.98</v>
+        <v>5.3</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V29" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR29" t="n">
         <v>32</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BT29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BZ29" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H30" t="n">
         <v>3.95</v>
@@ -7993,13 +7993,13 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>1.41</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
         <v>2.22</v>
@@ -8011,16 +8011,16 @@
         <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
@@ -8038,7 +8038,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD30" t="n">
         <v>16.5</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="AL30" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM30" t="n">
         <v>130</v>
@@ -8077,7 +8077,7 @@
         <v>70</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
         <v>11.5</v>
@@ -8086,10 +8086,10 @@
         <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
@@ -8122,7 +8122,7 @@
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF30" t="n">
         <v>19</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H31" t="n">
         <v>3.95</v>
@@ -8235,7 +8235,7 @@
         <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
         <v>5.2</v>
@@ -8247,7 +8247,7 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
@@ -8274,7 +8274,7 @@
         <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X31" t="n">
         <v>950</v>
@@ -8340,19 +8340,19 @@
         <v>2.08</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU31" t="n">
         <v>3.45</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AX31" t="n">
         <v>3.9</v>
@@ -8364,7 +8364,7 @@
         <v>4.1</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BB31" t="n">
         <v>4.2</v>
@@ -8373,16 +8373,16 @@
         <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BF31" t="n">
         <v>3.45</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
         <v>3.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>2.78</v>
@@ -8498,10 +8498,10 @@
         <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.61</v>
@@ -8513,7 +8513,7 @@
         <v>2.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S32" t="n">
         <v>5.7</v>
@@ -8525,7 +8525,7 @@
         <v>1.69</v>
       </c>
       <c r="V32" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
         <v>1.56</v>
@@ -8576,7 +8576,7 @@
         <v>90</v>
       </c>
       <c r="AM32" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
         <v>60</v>
@@ -8693,14 +8693,14 @@
         <v>2.1</v>
       </c>
       <c r="BZ32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
         <v>2.1</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -8791,10 +8791,10 @@
         <v>15</v>
       </c>
       <c r="Z33" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA33" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB33" t="n">
         <v>9.6</v>
@@ -8806,7 +8806,7 @@
         <v>22</v>
       </c>
       <c r="AE33" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF33" t="n">
         <v>15</v>
@@ -8818,25 +8818,25 @@
         <v>26</v>
       </c>
       <c r="AI33" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ33" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK33" t="n">
         <v>32</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM33" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN33" t="n">
         <v>27</v>
       </c>
       <c r="AO33" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP33" t="n">
         <v>8</v>
@@ -8866,7 +8866,7 @@
         <v>3.55</v>
       </c>
       <c r="AY33" t="n">
-        <v>8.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="AZ33" t="n">
         <v>4</v>
@@ -8878,7 +8878,7 @@
         <v>4.1</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="BD33" t="n">
         <v>4.3</v>
@@ -8887,7 +8887,7 @@
         <v>4.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="BG33" t="n">
         <v>4.5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>2.12</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I34" t="n">
         <v>6</v>
@@ -9000,7 +9000,7 @@
         <v>2.88</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.48</v>
@@ -9033,13 +9033,13 @@
         <v>1.72</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
         <v>1.89</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y34" t="n">
         <v>15</v>
@@ -9048,16 +9048,16 @@
         <v>42</v>
       </c>
       <c r="AA34" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE34" t="n">
         <v>110</v>
@@ -9069,7 +9069,7 @@
         <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI34" t="n">
         <v>130</v>
@@ -9084,13 +9084,13 @@
         <v>65</v>
       </c>
       <c r="AM34" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN34" t="n">
         <v>27</v>
       </c>
       <c r="AO34" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AP34" t="n">
         <v>3.65</v>
@@ -9099,52 +9099,52 @@
         <v>4</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS34" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW34" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AX34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ34" t="n">
         <v>4.6</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC34" t="n">
         <v>4.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH34" t="n">
         <v>2.88</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -866,7 +866,7 @@
         <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2.76</v>
@@ -884,7 +884,7 @@
         <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
         <v>2.04</v>
@@ -905,37 +905,37 @@
         <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
         <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>230</v>
       </c>
       <c r="AF2" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -944,25 +944,25 @@
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>6.6</v>
@@ -971,10 +971,10 @@
         <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -986,37 +986,37 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>2.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
@@ -1147,25 +1147,25 @@
         <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>17</v>
@@ -1174,13 +1174,13 @@
         <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>23</v>
@@ -1189,13 +1189,13 @@
         <v>370</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>380</v>
@@ -1207,31 +1207,31 @@
         <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
@@ -1240,19 +1240,19 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
@@ -1261,34 +1261,34 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>4.5</v>
@@ -1297,16 +1297,16 @@
         <v>3.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
@@ -1389,40 +1389,40 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
@@ -1431,16 +1431,16 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
         <v>65</v>
@@ -1449,100 +1449,100 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>60</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
         <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI4" t="n">
         <v>2.98</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11.5</v>
+        <v>1.58</v>
       </c>
       <c r="BN4" t="n">
         <v>6.8</v>
@@ -1554,16 +1554,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.4</v>
+        <v>1.69</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU4" t="n">
         <v>4.2</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1622,40 +1622,40 @@
         <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
         <v>3.3</v>
@@ -1664,13 +1664,13 @@
         <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1679,34 +1679,34 @@
         <v>24</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AA5" t="n">
         <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="n">
         <v>23</v>
@@ -1715,70 +1715,70 @@
         <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,19 +1897,19 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O6" t="n">
         <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
         <v>1.42</v>
@@ -1924,7 +1924,7 @@
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1939,10 +1939,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1951,10 +1951,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1963,70 +1963,70 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BF6" t="n">
         <v>1.69</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
         <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -2154,7 +2154,7 @@
         <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.1</v>
@@ -2175,25 +2175,25 @@
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
         <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="n">
         <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
@@ -2205,28 +2205,28 @@
         <v>400</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>8.800000000000001</v>
@@ -2235,16 +2235,16 @@
         <v>160</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -2253,10 +2253,10 @@
         <v>4.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX7" t="n">
         <v>5.6</v>
@@ -2265,28 +2265,28 @@
         <v>5.8</v>
       </c>
       <c r="AZ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -2387,52 +2387,52 @@
         <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I8" t="n">
         <v>2.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.24</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
         <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
         <v>18</v>
@@ -2480,7 +2480,7 @@
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN8" t="n">
         <v>25</v>
@@ -2489,49 +2489,49 @@
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
         <v>8.4</v>
@@ -2543,7 +2543,7 @@
         <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
         <v>2.96</v>
@@ -2552,19 +2552,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
         <v>22</v>
@@ -2576,35 +2576,35 @@
         <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.62</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>5.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV8" t="n">
         <v>19</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX8" t="n">
         <v>30</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>7.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2665,10 +2665,10 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2701,7 +2701,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AC9" t="n">
         <v>16.5</v>
@@ -2716,13 +2716,13 @@
         <v>180</v>
       </c>
       <c r="AG9" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2746,10 +2746,10 @@
         <v>5.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AS9" t="n">
         <v>4</v>
@@ -2761,37 +2761,37 @@
         <v>4.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>6</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB9" t="n">
         <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
         <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
         <v>3.15</v>
@@ -2800,46 +2800,46 @@
         <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ9" t="n">
         <v>16</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BN9" t="n">
         <v>19</v>
       </c>
       <c r="BO9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BT9" t="n">
         <v>3.65</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BW9" t="n">
         <v>4.1</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
         <v>13</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
         <v>1.96</v>
@@ -2913,13 +2913,13 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
         <v>1.6</v>
@@ -2940,7 +2940,7 @@
         <v>1.79</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2955,61 +2955,61 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU10" t="n">
         <v>5.1</v>
@@ -3018,37 +3018,37 @@
         <v>6.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AY10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5</v>
       </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BF10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>1.14</v>
       </c>
       <c r="G11" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
         <v>44</v>
@@ -3167,16 +3167,16 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3194,7 +3194,7 @@
         <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3233,7 +3233,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -3245,64 +3245,64 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BB11" t="n">
         <v>1.07</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BF11" t="n">
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>5.8</v>
@@ -3418,19 +3418,19 @@
         <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
@@ -3457,34 +3457,34 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF12" t="n">
         <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ12" t="n">
         <v>970</v>
@@ -3493,70 +3493,70 @@
         <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.4</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BG12" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H13" t="n">
         <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -3696,13 +3696,13 @@
         <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,10 +3711,10 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
@@ -3726,10 +3726,10 @@
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3738,37 +3738,37 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
         <v>85</v>
       </c>
-      <c r="AN13" t="n">
-        <v>970</v>
-      </c>
       <c r="AO13" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3777,10 +3777,10 @@
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3789,19 +3789,19 @@
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
         <v>6.2</v>
@@ -3810,7 +3810,7 @@
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="n">
         <v>4.4</v>
@@ -3831,7 +3831,7 @@
         <v>1.85</v>
       </c>
       <c r="BN13" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BO13" t="n">
         <v>4.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
         <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
@@ -3935,16 +3935,16 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
         <v>1.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
         <v>1.63</v>
@@ -3953,13 +3953,13 @@
         <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -3968,7 +3968,7 @@
         <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3980,10 +3980,10 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,85 +3992,85 @@
         <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.22</v>
+        <v>3.35</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.76</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.78</v>
+        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.26</v>
+        <v>3.65</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BH14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4100,7 +4100,7 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,7 +4112,7 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4124,11 +4124,11 @@
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -4198,13 +4198,13 @@
         <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
         <v>1.92</v>
@@ -4213,7 +4213,7 @@
         <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
         <v>14.5</v>
@@ -4240,46 +4240,46 @@
         <v>34</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH15" t="n">
         <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="AK15" t="n">
         <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
         <v>60</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
         <v>5.6</v>
@@ -4288,37 +4288,37 @@
         <v>6.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF15" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="n">
         <v>4.8</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -4437,31 +4437,31 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
         <v>1.5</v>
@@ -4470,79 +4470,79 @@
         <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z16" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
         <v>60</v>
       </c>
       <c r="AI16" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
         <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -4557,19 +4557,19 @@
         <v>3.85</v>
       </c>
       <c r="BB16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG16" t="n">
         <v>4.1</v>
@@ -4584,13 +4584,13 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>3.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
         <v>2.46</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
@@ -4697,13 +4697,13 @@
         <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
         <v>2.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
         <v>4.7</v>
@@ -4712,7 +4712,7 @@
         <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
         <v>1.57</v>
@@ -4742,7 +4742,7 @@
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
         <v>70</v>
@@ -4751,7 +4751,7 @@
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI17" t="n">
         <v>290</v>
@@ -4760,16 +4760,16 @@
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
         <v>380</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
         <v>60</v>
@@ -4784,7 +4784,7 @@
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
@@ -4796,34 +4796,34 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BE17" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG17" t="n">
         <v>21</v>
@@ -4850,7 +4850,7 @@
         <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="G18" t="n">
         <v>2.48</v>
       </c>
       <c r="H18" t="n">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -4936,7 +4936,7 @@
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4972,7 +4972,7 @@
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4987,10 +4987,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -4999,10 +4999,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -5011,76 +5011,76 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
         <v>1.33</v>
@@ -5199,7 +5199,7 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>1.26</v>
@@ -5208,10 +5208,10 @@
         <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
         <v>2.78</v>
@@ -5223,118 +5223,118 @@
         <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G20" t="n">
         <v>1.35</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K20" t="n">
         <v>6.6</v>
@@ -5474,22 +5474,22 @@
         <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
         <v>3.85</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Z20" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AA20" t="n">
         <v>460</v>
@@ -5498,10 +5498,10 @@
         <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD20" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AE20" t="n">
         <v>200</v>
@@ -5513,22 +5513,22 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AI20" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AN20" t="n">
         <v>4.7</v>
@@ -5540,55 +5540,55 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV20" t="n">
         <v>8</v>
       </c>
-      <c r="AU20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE20" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
         <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="n">
         <v>4.8</v>
@@ -5615,10 +5615,10 @@
         <v>3.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR20" t="n">
         <v>23</v>
@@ -5627,7 +5627,7 @@
         <v>6.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU20" t="n">
         <v>5.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G21" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.19</v>
@@ -5707,7 +5707,7 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.13</v>
@@ -5716,10 +5716,10 @@
         <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S21" t="n">
         <v>1.99</v>
@@ -5734,16 +5734,16 @@
         <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X21" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="n">
         <v>46</v>
       </c>
       <c r="Z21" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="AA21" t="n">
         <v>210</v>
@@ -5752,55 +5752,55 @@
         <v>18</v>
       </c>
       <c r="AC21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD21" t="n">
         <v>34</v>
       </c>
       <c r="AE21" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF21" t="n">
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO21" t="n">
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.1</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -5812,19 +5812,19 @@
         <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.3</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
         <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -5836,13 +5836,13 @@
         <v>18.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF21" t="n">
         <v>3.85</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="BH21" t="n">
         <v>5.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -5940,13 +5940,13 @@
         <v>2.28</v>
       </c>
       <c r="G22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H22" t="n">
         <v>2.86</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.84</v>
-      </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
         <v>2.92</v>
@@ -5967,7 +5967,7 @@
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
         <v>2.04</v>
@@ -5982,121 +5982,121 @@
         <v>1.56</v>
       </c>
       <c r="U22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
         <v>1.01</v>
       </c>
       <c r="R23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6239,118 +6239,118 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -6445,52 +6445,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G24" t="n">
         <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I24" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -6499,61 +6499,61 @@
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
         <v>13</v>
       </c>
       <c r="AE24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF24" t="n">
         <v>28</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>32</v>
       </c>
       <c r="AG24" t="n">
         <v>18</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>7.6</v>
@@ -6565,49 +6565,49 @@
         <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX24" t="n">
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI24" t="n">
         <v>2.8</v>
@@ -6616,13 +6616,13 @@
         <v>10</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6634,16 +6634,16 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
         <v>7.8</v>
       </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BT24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU24" t="n">
         <v>4</v>
@@ -6652,23 +6652,23 @@
         <v>17</v>
       </c>
       <c r="BW24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -6699,28 +6699,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="H25" t="n">
         <v>1.55</v>
       </c>
       <c r="I25" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
         <v>2.86</v>
@@ -6735,13 +6735,13 @@
         <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
         <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
         <v>1.63</v>
@@ -6756,13 +6756,13 @@
         <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB25" t="n">
         <v>950</v>
@@ -6771,43 +6771,43 @@
         <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
         <v>75</v>
       </c>
       <c r="AG25" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH25" t="n">
         <v>950</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AK25" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AL25" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AM25" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AN25" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>5.2</v>
@@ -6822,7 +6822,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
         <v>8.199999999999999</v>
@@ -6831,37 +6831,37 @@
         <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD25" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG25" t="n">
         <v>10</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI25" t="n">
         <v>2.48</v>
@@ -6876,53 +6876,53 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN25" t="n">
         <v>12</v>
       </c>
       <c r="BO25" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT25" t="n">
         <v>3.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BV25" t="n">
         <v>11.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>1.95</v>
       </c>
       <c r="G27" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
         <v>1.94</v>
@@ -7267,10 +7267,10 @@
         <v>15.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AA27" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
         <v>8</v>
@@ -7291,28 +7291,28 @@
         <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
         <v>24</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL27" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
         <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AP27" t="n">
         <v>9.199999999999999</v>
@@ -7321,10 +7321,10 @@
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -7336,7 +7336,7 @@
         <v>16.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
         <v>8</v>
@@ -7345,10 +7345,10 @@
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -7357,16 +7357,16 @@
         <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
         <v>11.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         <v>2.24</v>
       </c>
       <c r="I28" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -7479,31 +7479,31 @@
         <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R28" t="n">
         <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -7512,7 +7512,7 @@
         <v>1.64</v>
       </c>
       <c r="W28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
         <v>970</v>
@@ -7524,7 +7524,7 @@
         <v>970</v>
       </c>
       <c r="AA28" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>970</v>
@@ -7536,10 +7536,10 @@
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AG28" t="n">
         <v>970</v>
@@ -7548,79 +7548,79 @@
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AS28" t="n">
         <v>4.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AW28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE28" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB28" t="n">
+      <c r="BF28" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG28" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BH28" t="n">
         <v>5.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
         <v>1.69</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
@@ -7778,10 +7778,10 @@
         <v>70</v>
       </c>
       <c r="AA29" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC29" t="n">
         <v>11</v>
@@ -7793,10 +7793,10 @@
         <v>150</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
         <v>32</v>
@@ -7805,76 +7805,76 @@
         <v>140</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AN29" t="n">
         <v>15.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH29" t="n">
         <v>3.25</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -7969,34 +7969,34 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>4.1</v>
       </c>
       <c r="J30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.3</v>
       </c>
-      <c r="K30" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P30" t="n">
         <v>1.79</v>
@@ -8011,10 +8011,10 @@
         <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
         <v>1.32</v>
@@ -8038,19 +8038,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD30" t="n">
         <v>16.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH30" t="n">
         <v>19</v>
@@ -8068,7 +8068,7 @@
         <v>44</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
         <v>23</v>
@@ -8086,7 +8086,7 @@
         <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -8107,10 +8107,10 @@
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BB30" t="n">
         <v>25</v>
@@ -8122,7 +8122,7 @@
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BF30" t="n">
         <v>19</v>
@@ -8140,13 +8140,13 @@
         <v>11</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN30" t="n">
         <v>5</v>
@@ -8164,7 +8164,7 @@
         <v>36</v>
       </c>
       <c r="BS30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT30" t="n">
         <v>7.4</v>
@@ -8173,7 +8173,7 @@
         <v>6</v>
       </c>
       <c r="BV30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW30" t="n">
         <v>8.199999999999999</v>
@@ -8188,11 +8188,11 @@
         <v>36</v>
       </c>
       <c r="CA30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>1.76</v>
       </c>
       <c r="G31" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H31" t="n">
         <v>3.95</v>
@@ -8235,7 +8235,7 @@
         <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
         <v>5.2</v>
@@ -8283,10 +8283,10 @@
         <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
         <v>970</v>
@@ -8298,7 +8298,7 @@
         <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
         <v>970</v>
@@ -8310,79 +8310,79 @@
         <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>970</v>
       </c>
       <c r="AO31" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AT31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU31" t="n">
         <v>3.7</v>
       </c>
-      <c r="AU31" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AV31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX31" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>3.9</v>
       </c>
       <c r="AY31" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -8486,10 +8486,10 @@
         <v>3.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J32" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K32" t="n">
         <v>3.15</v>
@@ -8507,13 +8507,13 @@
         <v>1.61</v>
       </c>
       <c r="P32" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q32" t="n">
         <v>2.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S32" t="n">
         <v>5.7</v>
@@ -8522,7 +8522,7 @@
         <v>2.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
         <v>1.36</v>
@@ -8537,7 +8537,7 @@
         <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
         <v>95</v>
@@ -8552,7 +8552,7 @@
         <v>19</v>
       </c>
       <c r="AE32" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF32" t="n">
         <v>17.5</v>
@@ -8561,16 +8561,16 @@
         <v>15.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI32" t="n">
         <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL32" t="n">
         <v>90</v>
@@ -8585,76 +8585,76 @@
         <v>110</v>
       </c>
       <c r="AP32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU32" t="n">
         <v>3.25</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS32" t="n">
+      <c r="AV32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF32" t="n">
         <v>5</v>
       </c>
-      <c r="AT32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE32" t="n">
+      <c r="BG32" t="n">
         <v>5.2</v>
       </c>
-      <c r="BF32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>5</v>
-      </c>
       <c r="BH32" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="BJ32" t="n">
         <v>12</v>
       </c>
       <c r="BK32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="BN32" t="n">
         <v>5.4</v>
@@ -8666,13 +8666,13 @@
         <v>25</v>
       </c>
       <c r="BQ32" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR32" t="n">
         <v>55</v>
       </c>
       <c r="BS32" t="n">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="BT32" t="n">
         <v>6.6</v>
@@ -8681,26 +8681,26 @@
         <v>4.4</v>
       </c>
       <c r="BV32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW32" t="n">
-        <v>2.06</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G33" t="n">
         <v>2.22</v>
@@ -8740,10 +8740,10 @@
         <v>3.95</v>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
@@ -8758,7 +8758,7 @@
         <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
         <v>1.67</v>
@@ -8767,7 +8767,7 @@
         <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
         <v>4.4</v>
@@ -8824,7 +8824,7 @@
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
@@ -8842,10 +8842,10 @@
         <v>8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AS33" t="n">
         <v>4.6</v>
@@ -8857,43 +8857,43 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW33" t="n">
         <v>4.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>4</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC33" t="n">
         <v>4.1</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE33" t="n">
         <v>4.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH33" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI33" t="n">
         <v>2.52</v>
@@ -8902,7 +8902,7 @@
         <v>970</v>
       </c>
       <c r="BK33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
@@ -8914,31 +8914,31 @@
         <v>4.7</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
@@ -8950,11 +8950,11 @@
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>4.1</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J34" t="n">
         <v>2.88</v>
@@ -9003,13 +9003,13 @@
         <v>3.55</v>
       </c>
       <c r="L34" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
@@ -9018,7 +9018,7 @@
         <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
@@ -9048,7 +9048,7 @@
         <v>42</v>
       </c>
       <c r="AA34" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
         <v>7.2</v>
@@ -9066,7 +9066,7 @@
         <v>12.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH34" t="n">
         <v>28</v>
@@ -9075,10 +9075,10 @@
         <v>130</v>
       </c>
       <c r="AJ34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK34" t="n">
         <v>29</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>32</v>
       </c>
       <c r="AL34" t="n">
         <v>65</v>
@@ -9093,64 +9093,64 @@
         <v>700</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AQ34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY34" t="n">
         <v>4</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AZ34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS34" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC34" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH34" t="n">
         <v>2.88</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ34" t="n">
         <v>12</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -1010,7 +1010,7 @@
         <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>130</v>
       </c>
       <c r="BF2" t="n">
         <v>6.8</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
         <v>6.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -1135,16 +1135,16 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
         <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -1159,16 +1159,16 @@
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
         <v>42</v>
@@ -1177,19 +1177,19 @@
         <v>700</v>
       </c>
       <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
         <v>8</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>370</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1201,7 +1201,7 @@
         <v>380</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="n">
         <v>27</v>
@@ -1225,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1237,10 +1237,10 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
@@ -1249,10 +1249,10 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
@@ -1270,7 +1270,7 @@
         <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1294,13 +1294,13 @@
         <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
         <v>6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
         <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
@@ -1395,10 +1395,10 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
@@ -1413,16 +1413,16 @@
         <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
@@ -1437,7 +1437,7 @@
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
@@ -1482,7 +1482,7 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4" t="n">
         <v>11.5</v>
@@ -1509,7 +1509,7 @@
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
@@ -1524,13 +1524,13 @@
         <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1637,13 +1637,13 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
@@ -1661,16 +1661,16 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1682,10 +1682,10 @@
         <v>140</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
         <v>8.6</v>
@@ -1703,28 +1703,28 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
         <v>320</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
         <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>12</v>
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
@@ -1751,7 +1751,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
@@ -1763,10 +1763,10 @@
         <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
         <v>26</v>
@@ -1775,28 +1775,28 @@
         <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
         <v>4.4</v>
@@ -1805,44 +1805,44 @@
         <v>3.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
@@ -1897,7 +1897,7 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.15</v>
@@ -1924,7 +1924,7 @@
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
         <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -2151,7 +2151,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
@@ -2172,7 +2172,7 @@
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
         <v>1.19</v>
@@ -2184,7 +2184,7 @@
         <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z7" t="n">
         <v>60</v>
@@ -2196,10 +2196,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>400</v>
@@ -2214,10 +2214,10 @@
         <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="n">
         <v>17.5</v>
@@ -2229,22 +2229,22 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
         <v>160</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -2253,46 +2253,46 @@
         <v>4.9</v>
       </c>
       <c r="AV7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2387,70 +2387,70 @@
         <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
         <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
         <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>12.5</v>
@@ -2468,25 +2468,25 @@
         <v>16.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>6.4</v>
@@ -2495,64 +2495,64 @@
         <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
         <v>17.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2567,44 +2567,44 @@
         <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ8" t="n">
         <v>7.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
         <v>7</v>
       </c>
       <c r="BX8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2635,175 +2635,175 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="G9" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
         <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
         <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>440</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL9" t="n">
         <v>150</v>
       </c>
-      <c r="AH9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>400</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>290</v>
       </c>
-      <c r="AM9" t="n">
-        <v>350</v>
-      </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AP9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5</v>
-      </c>
       <c r="AX9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>6</v>
       </c>
       <c r="BA9" t="n">
         <v>6.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BK9" t="n">
         <v>5.9</v>
@@ -2812,10 +2812,10 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BO9" t="n">
         <v>6.2</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.58</v>
+        <v>1.59</v>
       </c>
       <c r="BT9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I10" t="n">
         <v>2.26</v>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -2913,13 +2913,13 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
         <v>1.6</v>
@@ -2928,19 +2928,19 @@
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>1.79</v>
       </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2949,7 +2949,7 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2997,19 +2997,19 @@
         <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
         <v>5.1</v>
@@ -3018,55 +3018,55 @@
         <v>6.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG10" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="H11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>5.7</v>
       </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>44</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -3403,16 +3403,16 @@
         <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
@@ -3421,16 +3421,16 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
@@ -3439,7 +3439,7 @@
         <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
         <v>2.12</v>
@@ -3448,7 +3448,7 @@
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3505,76 +3505,76 @@
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR12" t="n">
         <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.94</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.34</v>
+        <v>1.88</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
@@ -3592,35 +3592,35 @@
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.34</v>
+        <v>1.88</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
         <v>4.3</v>
@@ -3663,7 +3663,7 @@
         <v>5.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -3672,10 +3672,10 @@
         <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.2</v>
@@ -3687,10 +3687,10 @@
         <v>1.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
         <v>1.63</v>
@@ -3702,7 +3702,7 @@
         <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3723,13 +3723,13 @@
         <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3759,16 +3759,16 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>6</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3780,7 +3780,7 @@
         <v>5.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3789,28 +3789,28 @@
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB13" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.4</v>
@@ -3822,59 +3822,59 @@
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="BN13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -3911,10 +3911,10 @@
         <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
@@ -3929,28 +3929,28 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
         <v>1.66</v>
@@ -4022,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.4</v>
@@ -4046,61 +4046,61 @@
         <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
       </c>
       <c r="BG14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI14" t="n">
         <v>3.3</v>
       </c>
-      <c r="BH14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -4168,64 +4168,64 @@
         <v>1.89</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
         <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
         <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>29</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
         <v>25</v>
       </c>
       <c r="AB15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC15" t="n">
         <v>11</v>
@@ -4261,128 +4261,128 @@
         <v>60</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU15" t="n">
         <v>9</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AV15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG15" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH15" t="n">
         <v>4.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ15" t="n">
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN15" t="n">
         <v>8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR15" t="n">
         <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BV15" t="n">
         <v>13.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>14.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
         <v>2.44</v>
@@ -4425,10 +4425,10 @@
         <v>2.74</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -4437,19 +4437,19 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
         <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
         <v>2.4</v>
@@ -4461,16 +4461,16 @@
         <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
         <v>500</v>
@@ -4479,13 +4479,13 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
         <v>80</v>
@@ -4494,7 +4494,7 @@
         <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>60</v>
@@ -4503,7 +4503,7 @@
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
         <v>500</v>
@@ -4515,22 +4515,22 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4539,10 +4539,10 @@
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -4554,43 +4554,43 @@
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BB16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4</v>
       </c>
-      <c r="BC16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BE16" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
         <v>3.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4602,7 +4602,7 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4626,7 +4626,7 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
@@ -4691,10 +4691,10 @@
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P17" t="n">
         <v>1.65</v>
@@ -4712,7 +4712,7 @@
         <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
         <v>1.57</v>
@@ -4730,19 +4730,19 @@
         <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB17" t="n">
         <v>10</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
         <v>70</v>
@@ -4754,10 +4754,10 @@
         <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
         <v>500</v>
@@ -4769,10 +4769,10 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
         <v>9.800000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -4796,10 +4796,10 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
         <v>12.5</v>
@@ -4808,13 +4808,13 @@
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BD17" t="n">
         <v>28</v>
@@ -4823,10 +4823,10 @@
         <v>11.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="n">
         <v>2.88</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5211,10 +5211,10 @@
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
         <v>1.4</v>
@@ -5226,7 +5226,7 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="H20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -5453,7 +5453,7 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.18</v>
@@ -5468,19 +5468,19 @@
         <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
         <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V20" t="n">
         <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="X20" t="n">
         <v>48</v>
@@ -5507,7 +5507,7 @@
         <v>200</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
@@ -5531,40 +5531,40 @@
         <v>380</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="AR20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW20" t="n">
         <v>8</v>
       </c>
-      <c r="AS20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AX20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
@@ -5573,13 +5573,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
         <v>8.199999999999999</v>
@@ -5588,10 +5588,10 @@
         <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI20" t="n">
         <v>3.65</v>
@@ -5600,59 +5600,59 @@
         <v>12.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
         <v>4.1</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BP20" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BR20" t="n">
         <v>23</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT20" t="n">
         <v>15</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G21" t="n">
         <v>1.46</v>
@@ -5698,7 +5698,7 @@
         <v>5.5</v>
       </c>
       <c r="K21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.19</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
         <v>1.56</v>
       </c>
       <c r="U22" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
@@ -6006,7 +6006,7 @@
         <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD22" t="n">
         <v>950</v>
@@ -6045,58 +6045,58 @@
         <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H23" t="n">
         <v>2.3</v>
@@ -6278,7 +6278,7 @@
         <v>950</v>
       </c>
       <c r="AI23" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ23" t="n">
         <v>900</v>
@@ -6299,58 +6299,58 @@
         <v>500</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
         <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
         <v>6.4</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="G25" t="n">
         <v>8.6</v>
@@ -6777,10 +6777,10 @@
         <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH25" t="n">
         <v>950</v>
@@ -6789,19 +6789,19 @@
         <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AK25" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AL25" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AM25" t="n">
         <v>700</v>
       </c>
       <c r="AN25" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
@@ -6831,31 +6831,31 @@
         <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ25" t="n">
         <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
         <v>13.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6900,13 +6900,13 @@
         <v>3.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BV25" t="n">
         <v>11.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>1.95</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="n">
         <v>15.5</v>
@@ -7273,19 +7273,19 @@
         <v>900</v>
       </c>
       <c r="AB27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
         <v>8</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG27" t="n">
         <v>11</v>
@@ -7297,10 +7297,10 @@
         <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AK27" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>500</v>
@@ -7309,16 +7309,16 @@
         <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO27" t="n">
         <v>500</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
         <v>8</v>
@@ -7327,46 +7327,46 @@
         <v>9.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW27" t="n">
         <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
         <v>6.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
         <v>11.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
         <v>3.95</v>
@@ -7470,22 +7470,22 @@
         <v>2.24</v>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>1.36</v>
@@ -7494,19 +7494,19 @@
         <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V28" t="n">
         <v>1.64</v>
@@ -7518,7 +7518,7 @@
         <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
         <v>970</v>
@@ -7530,7 +7530,7 @@
         <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7545,7 +7545,7 @@
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -7569,58 +7569,58 @@
         <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4</v>
-      </c>
       <c r="BA28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG28" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>3.8</v>
       </c>
       <c r="BH28" t="n">
         <v>5.5</v>
@@ -7644,7 +7644,7 @@
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
@@ -7662,7 +7662,7 @@
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7680,11 +7680,11 @@
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>1.75</v>
       </c>
       <c r="H29" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
         <v>7.4</v>
@@ -7730,7 +7730,7 @@
         <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.38</v>
@@ -7739,28 +7739,28 @@
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
         <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V29" t="n">
         <v>1.16</v>
@@ -7823,55 +7823,55 @@
         <v>700</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS29" t="n">
         <v>5.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AW29" t="n">
         <v>5.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
         <v>5.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE29" t="n">
         <v>5.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
         <v>5.7</v>
@@ -7880,7 +7880,7 @@
         <v>3.25</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="BJ29" t="n">
         <v>12</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
@@ -8053,7 +8053,7 @@
         <v>10.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI30" t="n">
         <v>70</v>
@@ -8071,7 +8071,7 @@
         <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>70</v>
@@ -8080,13 +8080,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -8095,7 +8095,7 @@
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW30" t="n">
         <v>46</v>
@@ -8110,7 +8110,7 @@
         <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>25</v>
@@ -8122,7 +8122,7 @@
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BF30" t="n">
         <v>19</v>
@@ -8134,7 +8134,7 @@
         <v>3.15</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ30" t="n">
         <v>11</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>2.08</v>
       </c>
       <c r="G33" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H33" t="n">
         <v>3.95</v>
@@ -8746,10 +8746,10 @@
         <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
         <v>1.1</v>
@@ -8764,16 +8764,16 @@
         <v>1.67</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
         <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
         <v>1.78</v>
@@ -8782,7 +8782,7 @@
         <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
@@ -8812,10 +8812,10 @@
         <v>15</v>
       </c>
       <c r="AG33" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="AH33" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI33" t="n">
         <v>500</v>
@@ -8824,7 +8824,7 @@
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
@@ -8842,13 +8842,13 @@
         <v>8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
@@ -8857,40 +8857,40 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AW33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB33" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC33" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH33" t="n">
         <v>2.98</v>
@@ -8908,7 +8908,7 @@
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="BN33" t="n">
         <v>4.7</v>
@@ -8926,7 +8926,7 @@
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
@@ -8938,7 +8938,7 @@
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
@@ -8950,11 +8950,11 @@
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H34" t="n">
         <v>4.1</v>
@@ -8997,7 +8997,7 @@
         <v>5.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K34" t="n">
         <v>3.55</v>
@@ -9009,7 +9009,7 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
@@ -9030,13 +9030,13 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V34" t="n">
         <v>1.22</v>
       </c>
       <c r="W34" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X34" t="n">
         <v>10.5</v>
@@ -9057,13 +9057,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE34" t="n">
         <v>110</v>
       </c>
       <c r="AF34" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG34" t="n">
         <v>12</v>
@@ -9093,58 +9093,58 @@
         <v>700</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX34" t="n">
         <v>4.1</v>
       </c>
       <c r="AY34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BA34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD34" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE34" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH34" t="n">
         <v>2.88</v>
@@ -9195,7 +9195,7 @@
         <v>2.2</v>
       </c>
       <c r="BX34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY34" t="n">
         <v>2.22</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -860,16 +860,16 @@
         <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
@@ -887,7 +887,7 @@
         <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
@@ -908,13 +908,13 @@
         <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="Z2" t="n">
         <v>970</v>
@@ -923,13 +923,13 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>230</v>
@@ -974,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -986,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
         <v>9</v>
@@ -998,31 +998,31 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
         <v>130</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="n">
         <v>2.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1055,7 +1055,7 @@
         <v>1.51</v>
       </c>
       <c r="BT2" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BU2" t="n">
         <v>3.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1111,40 +1111,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -1153,25 +1153,25 @@
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
         <v>700</v>
@@ -1189,13 +1189,13 @@
         <v>370</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>380</v>
@@ -1204,10 +1204,10 @@
         <v>90</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1225,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1240,22 +1240,22 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
@@ -1264,77 +1264,77 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
@@ -1410,55 +1410,55 @@
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
         <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
@@ -1467,40 +1467,40 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>9</v>
@@ -1509,10 +1509,10 @@
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
         <v>20</v>
@@ -1521,16 +1521,16 @@
         <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1554,7 +1554,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1578,7 +1578,7 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1619,40 +1619,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
         <v>4.1</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
@@ -1661,188 +1661,188 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.26</v>
+        <v>3.55</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="AI5" t="n">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="AN5" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA5" t="n">
         <v>12</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>12</v>
       </c>
-      <c r="AW5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13.5</v>
+        <v>150</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BO5" t="n">
         <v>3.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>1.46</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
         <v>55</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>15.5</v>
@@ -1900,7 +1900,7 @@
         <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
@@ -1912,7 +1912,7 @@
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
         <v>5.3</v>
@@ -2217,10 +2217,10 @@
         <v>320</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
@@ -2229,34 +2229,34 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO7" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP7" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7" t="n">
         <v>9.199999999999999</v>
@@ -2265,28 +2265,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
         <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
         <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2411,10 +2411,10 @@
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
@@ -2426,16 +2426,16 @@
         <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
@@ -2450,13 +2450,13 @@
         <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
         <v>22</v>
@@ -2489,28 +2489,28 @@
         <v>22</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AX8" t="n">
         <v>17.5</v>
@@ -2522,25 +2522,25 @@
         <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
         <v>3.65</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -2635,73 +2635,73 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="H9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.33</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.43</v>
-      </c>
       <c r="J9" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
         <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z9" t="n">
         <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
         <v>15.5</v>
@@ -2710,155 +2710,155 @@
         <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AG9" t="n">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="AH9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="AL9" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AM9" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN9" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AP9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="BD9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK9" t="n">
         <v>5.7</v>
       </c>
-      <c r="AU9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BO9" t="n">
         <v>6</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.59</v>
+        <v>2.66</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.59</v>
+        <v>2.64</v>
       </c>
       <c r="BT9" t="n">
         <v>3.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BX9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -2949,7 +2949,7 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2973,7 +2973,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -3003,13 +3003,13 @@
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS10" t="n">
         <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>5.1</v>
@@ -3018,37 +3018,37 @@
         <v>6.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
         <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -3143,58 +3143,58 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.29</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="H11" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.05</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="X11" t="n">
         <v>970</v>
@@ -3203,16 +3203,16 @@
         <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
         <v>950</v>
@@ -3221,22 +3221,22 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
@@ -3245,76 +3245,76 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BI11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3329,16 +3329,16 @@
         <v>2.94</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H12" t="n">
         <v>5.3</v>
@@ -3409,7 +3409,7 @@
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
         <v>7</v>
@@ -3418,7 +3418,7 @@
         <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>4.5</v>
@@ -3427,16 +3427,16 @@
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
         <v>1.8</v>
@@ -3505,55 +3505,55 @@
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR12" t="n">
         <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
         <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BA12" t="n">
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BG12" t="n">
         <v>4.2</v>
@@ -3562,31 +3562,31 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3598,29 +3598,29 @@
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -3651,55 +3651,55 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
         <v>1.86</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.55</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.63</v>
-      </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>2.16</v>
@@ -3729,13 +3729,13 @@
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
@@ -3753,22 +3753,22 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3777,10 +3777,10 @@
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3789,37 +3789,37 @@
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
         <v>4.8</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.94</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.72</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I14" t="n">
         <v>2.52</v>
@@ -3920,49 +3920,49 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
         <v>970</v>
@@ -3974,10 +3974,10 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
         <v>500</v>
@@ -4013,7 +4013,7 @@
         <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
@@ -4022,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.4</v>
@@ -4034,10 +4034,10 @@
         <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
@@ -4046,61 +4046,61 @@
         <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>1.6</v>
       </c>
-      <c r="BN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.52</v>
-      </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>4.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I15" t="n">
         <v>2.06</v>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.22</v>
@@ -4189,7 +4189,7 @@
         <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q15" t="n">
         <v>1.5</v>
@@ -4198,10 +4198,10 @@
         <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="T15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
         <v>2.6</v>
@@ -4249,7 +4249,7 @@
         <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="n">
         <v>40</v>
@@ -4279,7 +4279,7 @@
         <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>9</v>
@@ -4330,7 +4330,7 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4345,10 +4345,10 @@
         <v>5.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
         <v>32</v>
@@ -4369,7 +4369,7 @@
         <v>5.6</v>
       </c>
       <c r="BX15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY15" t="n">
         <v>6.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -4437,34 +4437,34 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
         <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
         <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4506,7 +4506,7 @@
         <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -4518,31 +4518,31 @@
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AV16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -4554,43 +4554,43 @@
         <v>9</v>
       </c>
       <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF16" t="n">
         <v>3.8</v>
       </c>
-      <c r="BB16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>2.46</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.65</v>
@@ -4691,7 +4691,7 @@
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
         <v>1.47</v>
@@ -4730,7 +4730,7 @@
         <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="n">
         <v>10</v>
@@ -4808,13 +4808,13 @@
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>28</v>
@@ -4826,7 +4826,7 @@
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="n">
         <v>2.88</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -4921,94 +4921,94 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
-        <v>2.54</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>500</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>1.34</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>970</v>
       </c>
       <c r="AC18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD18" t="n">
         <v>950</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF18" t="n">
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ18" t="n">
         <v>900</v>
@@ -5020,25 +5020,25 @@
         <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.26</v>
+        <v>3.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="AT18" t="n">
         <v>5.8</v>
@@ -5047,40 +5047,40 @@
         <v>5.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.26</v>
+        <v>3.75</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.27</v>
+        <v>3.65</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.26</v>
+        <v>3.7</v>
       </c>
       <c r="AY18" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.27</v>
+        <v>3.15</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.23</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.22</v>
+        <v>4.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.26</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.27</v>
+        <v>3.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -5175,61 +5175,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="H19" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
         <v>970</v>
@@ -5241,25 +5241,25 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC19" t="n">
         <v>42</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
@@ -5277,22 +5277,22 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.88</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.88</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AT19" t="n">
         <v>5.8</v>
@@ -5301,104 +5301,104 @@
         <v>5.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.87</v>
+        <v>6.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.87</v>
+        <v>7</v>
       </c>
       <c r="AY19" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.91</v>
+        <v>6.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.96</v>
+        <v>6.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.93</v>
+        <v>6.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.96</v>
+        <v>2.86</v>
       </c>
       <c r="BE19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BF19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI19" t="n">
         <v>2.88</v>
       </c>
-      <c r="BG19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.8</v>
+        <v>1.39</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G20" t="n">
         <v>1.32</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
         <v>13.5</v>
@@ -5444,10 +5444,10 @@
         <v>5.9</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
@@ -5462,16 +5462,16 @@
         <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R20" t="n">
         <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
         <v>1.82</v>
@@ -5483,25 +5483,25 @@
         <v>4.1</v>
       </c>
       <c r="X20" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
         <v>460</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
         <v>15</v>
       </c>
       <c r="AD20" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AE20" t="n">
         <v>200</v>
@@ -5513,10 +5513,10 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AI20" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="AJ20" t="n">
         <v>11</v>
@@ -5528,25 +5528,25 @@
         <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AN20" t="n">
         <v>4.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT20" t="n">
         <v>8.6</v>
@@ -5555,10 +5555,10 @@
         <v>12</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>7.4</v>
@@ -5570,7 +5570,7 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
         <v>8.800000000000001</v>
@@ -5579,40 +5579,40 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
         <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH20" t="n">
         <v>4.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ20" t="n">
         <v>12.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
         <v>4.1</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP20" t="n">
         <v>7.6</v>
@@ -5642,17 +5642,17 @@
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -5689,13 +5689,13 @@
         <v>1.46</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K21" t="n">
         <v>6.2</v>
@@ -5707,31 +5707,31 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
         <v>1.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="T21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
         <v>3.15</v>
@@ -5791,122 +5791,122 @@
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AV21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9</v>
-      </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BH21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.7</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP21" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
         <v>11</v>
       </c>
       <c r="BU21" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -5937,166 +5937,166 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H22" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB22" t="n">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.19</v>
+        <v>8.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.18</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.17</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.16</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.18</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.19</v>
+        <v>11.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.17</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.19</v>
+        <v>7</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.19</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.19</v>
+        <v>8</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6245,7 +6245,7 @@
         <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y23" t="n">
         <v>950</v>
@@ -6302,7 +6302,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="AR23" t="n">
         <v>1.16</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -6445,52 +6445,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H24" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="I24" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J24" t="n">
         <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.06</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -6499,22 +6499,22 @@
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AA24" t="n">
         <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
         <v>13</v>
@@ -6526,10 +6526,10 @@
         <v>28</v>
       </c>
       <c r="AG24" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AI24" t="n">
         <v>500</v>
@@ -6544,13 +6544,13 @@
         <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>500</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -6565,13 +6565,13 @@
         <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
         <v>17.5</v>
@@ -6580,49 +6580,49 @@
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BB24" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
         <v>12.5</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6634,13 +6634,13 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT24" t="n">
         <v>5.3</v>
@@ -6649,26 +6649,26 @@
         <v>4</v>
       </c>
       <c r="BV24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW24" t="n">
         <v>6.2</v>
       </c>
       <c r="BX24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA24" t="n">
         <v>7.2</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -6717,16 +6717,16 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
@@ -6753,7 +6753,7 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y25" t="n">
         <v>6.2</v>
@@ -6765,7 +6765,7 @@
         <v>15.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AC25" t="n">
         <v>10.5</v>
@@ -6774,16 +6774,16 @@
         <v>11</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="n">
         <v>34</v>
       </c>
       <c r="AH25" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
@@ -6795,7 +6795,7 @@
         <v>200</v>
       </c>
       <c r="AL25" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="AM25" t="n">
         <v>700</v>
@@ -6831,31 +6831,31 @@
         <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AZ25" t="n">
         <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC25" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC25" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG25" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
         <v>13.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6900,16 +6900,16 @@
         <v>3.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BV25" t="n">
         <v>11.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY25" t="n">
         <v>8.4</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G27" t="n">
         <v>1.97</v>
@@ -7222,7 +7222,7 @@
         <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -7261,112 +7261,112 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>700</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW27" t="n">
         <v>12</v>
       </c>
-      <c r="AG27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="AX27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="BD27" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE27" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB27" t="n">
+      <c r="BF27" t="n">
         <v>16</v>
       </c>
-      <c r="BC27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG27" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>3.95</v>
       </c>
       <c r="H28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I28" t="n">
         <v>2.56</v>
@@ -7485,7 +7485,7 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.36</v>
@@ -7503,7 +7503,7 @@
         <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
         <v>1.99</v>
@@ -7515,10 +7515,10 @@
         <v>1.36</v>
       </c>
       <c r="X28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y28" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="Z28" t="n">
         <v>970</v>
@@ -7527,10 +7527,10 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7560,7 +7560,7 @@
         <v>500</v>
       </c>
       <c r="AM28" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
         <v>500</v>
@@ -7569,19 +7569,19 @@
         <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>7.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -7590,37 +7590,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD28" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BE28" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BH28" t="n">
         <v>5.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -7715,175 +7715,175 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="G29" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="H29" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="I29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB29" t="n">
         <v>7.4</v>
       </c>
-      <c r="J29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X29" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>450</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK29" t="n">
         <v>23</v>
       </c>
-      <c r="Z29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>21</v>
-      </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="n">
         <v>700</v>
       </c>
       <c r="AN29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>700</v>
       </c>
       <c r="AP29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AT29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
         <v>19</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE29" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="BJ29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK29" t="n">
         <v>5.8</v>
@@ -7892,53 +7892,53 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="BN29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BO29" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BP29" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT29" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW29" t="n">
-        <v>2.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.46</v>
+        <v>10</v>
       </c>
       <c r="BZ29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.32</v>
+        <v>8.4</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -7999,19 +7999,19 @@
         <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q30" t="n">
         <v>2.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
         <v>2.02</v>
@@ -8047,7 +8047,7 @@
         <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
         <v>10.5</v>
@@ -8086,13 +8086,13 @@
         <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
         <v>15</v>
@@ -8107,10 +8107,10 @@
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BB30" t="n">
         <v>25</v>
@@ -8122,7 +8122,7 @@
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="BF30" t="n">
         <v>19</v>
@@ -8140,7 +8140,7 @@
         <v>11</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8158,16 +8158,16 @@
         <v>18</v>
       </c>
       <c r="BQ30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR30" t="n">
         <v>36</v>
       </c>
       <c r="BS30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU30" t="n">
         <v>6</v>
@@ -8176,23 +8176,23 @@
         <v>36</v>
       </c>
       <c r="BW30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX30" t="n">
         <v>55</v>
       </c>
       <c r="BY30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ30" t="n">
         <v>36</v>
       </c>
       <c r="CA30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G31" t="n">
         <v>1.97</v>
@@ -8289,10 +8289,10 @@
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC31" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
@@ -8301,13 +8301,13 @@
         <v>500</v>
       </c>
       <c r="AF31" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG31" t="n">
         <v>970</v>
       </c>
       <c r="AH31" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
@@ -8322,67 +8322,67 @@
         <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO31" t="n">
         <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="AR31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.02</v>
+        <v>2.98</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AY31" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.02</v>
+        <v>2.98</v>
       </c>
       <c r="BB31" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.16</v>
+        <v>5.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BG31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
         <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
         <v>1.15</v>
@@ -8510,7 +8510,7 @@
         <v>1.46</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R32" t="n">
         <v>1.16</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>2.08</v>
       </c>
       <c r="G33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H33" t="n">
         <v>3.95</v>
@@ -8749,19 +8749,19 @@
         <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
         <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q33" t="n">
         <v>2.3</v>
@@ -8776,7 +8776,7 @@
         <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V33" t="n">
         <v>1.29</v>
@@ -8842,13 +8842,13 @@
         <v>8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS33" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
@@ -8857,58 +8857,58 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD33" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC33" t="n">
+      <c r="BE33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
         <v>2.98</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>2.26</v>
       </c>
       <c r="BN33" t="n">
         <v>4.7</v>
@@ -8920,41 +8920,41 @@
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G34" t="n">
         <v>2.14</v>
       </c>
       <c r="H34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I34" t="n">
         <v>5.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
         <v>3.55</v>
@@ -9018,13 +9018,13 @@
         <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="T34" t="n">
         <v>2.1</v>
@@ -9036,7 +9036,7 @@
         <v>1.22</v>
       </c>
       <c r="W34" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>10.5</v>
@@ -9063,7 +9063,7 @@
         <v>110</v>
       </c>
       <c r="AF34" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG34" t="n">
         <v>12</v>
@@ -9072,10 +9072,10 @@
         <v>28</v>
       </c>
       <c r="AI34" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK34" t="n">
         <v>29</v>
@@ -9087,128 +9087,128 @@
         <v>500</v>
       </c>
       <c r="AN34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO34" t="n">
         <v>700</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE34" t="n">
         <v>6</v>
       </c>
-      <c r="AT34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV34" t="n">
+      <c r="BF34" t="n">
         <v>5</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="BG34" t="n">
         <v>6</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH34" t="n">
         <v>2.88</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ34" t="n">
         <v>12</v>
       </c>
       <c r="BK34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BN34" t="n">
         <v>4.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP34" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ34" t="n">
         <v>6.6</v>
       </c>
       <c r="BR34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS34" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BT34" t="n">
         <v>8.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV34" t="n">
         <v>55</v>
       </c>
       <c r="BW34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY34" t="n">
         <v>2.2</v>
       </c>
-      <c r="BX34" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BZ34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -857,100 +857,100 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.52</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK2" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AL2" t="n">
         <v>450</v>
@@ -965,122 +965,122 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU2" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2" t="n">
         <v>130</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
         <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.48</v>
+        <v>8.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.51</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.51</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1111,88 +1111,88 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="G3" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.94</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.92</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA3" t="n">
         <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>370</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
@@ -1204,7 +1204,7 @@
         <v>90</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
         <v>190</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
@@ -1222,61 +1222,61 @@
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
         <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>140</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
         <v>3.95</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA3" t="n">
         <v>10</v>
       </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1383,40 +1383,40 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
         <v>17</v>
@@ -1425,10 +1425,10 @@
         <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
         <v>22</v>
@@ -1455,7 +1455,7 @@
         <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AK4" t="n">
         <v>100</v>
@@ -1470,7 +1470,7 @@
         <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
         <v>8.4</v>
@@ -1482,13 +1482,13 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>9.4</v>
@@ -1497,19 +1497,19 @@
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>30</v>
@@ -1518,7 +1518,7 @@
         <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1536,31 +1536,31 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.58</v>
+        <v>85</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BT4" t="n">
         <v>5.3</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1619,175 +1619,175 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="G5" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="H5" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Z5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>14</v>
-      </c>
       <c r="AX5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD5" t="n">
         <v>29</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
       </c>
       <c r="BE5" t="n">
         <v>120</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
         <v>7</v>
@@ -1802,47 +1802,47 @@
         <v>3.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>1.46</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -2032,7 +2032,7 @@
         <v>1.69</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>14.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -2157,40 +2157,40 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
         <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
         <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
         <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="n">
         <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>9.800000000000001</v>
@@ -2199,19 +2199,19 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>400</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>320</v>
@@ -2226,7 +2226,7 @@
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
         <v>9.199999999999999</v>
@@ -2241,10 +2241,10 @@
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>8.199999999999999</v>
@@ -2256,7 +2256,7 @@
         <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
         <v>9.199999999999999</v>
@@ -2265,10 +2265,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
         <v>14</v>
@@ -2277,16 +2277,16 @@
         <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2298,59 +2298,59 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BN7" t="n">
         <v>4.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP7" t="n">
         <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G8" t="n">
         <v>3.2</v>
@@ -2390,13 +2390,13 @@
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2417,7 +2417,7 @@
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
         <v>3.15</v>
@@ -2429,10 +2429,10 @@
         <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
         <v>15.5</v>
@@ -2444,13 +2444,13 @@
         <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="n">
         <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
         <v>12.5</v>
@@ -2480,7 +2480,7 @@
         <v>85</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN8" t="n">
         <v>27</v>
@@ -2498,10 +2498,10 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
@@ -2516,31 +2516,31 @@
         <v>17.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>3.65</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2635,64 +2635,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>13.5</v>
       </c>
       <c r="H9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L9" t="n">
         <v>1.28</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.32</v>
-      </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
         <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z9" t="n">
         <v>8</v>
@@ -2704,7 +2704,7 @@
         <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2713,10 +2713,10 @@
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AH9" t="n">
         <v>85</v>
@@ -2728,94 +2728,94 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="AL9" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
         <v>280</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH9" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BO9" t="n">
         <v>6</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.64</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY9" t="n">
         <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2925,7 +2925,7 @@
         <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
         <v>2.5</v>
@@ -2937,7 +2937,7 @@
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W10" t="n">
         <v>1.33</v>
@@ -2949,7 +2949,7 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2973,7 +2973,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -3003,13 +3003,13 @@
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AS10" t="n">
         <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
         <v>5.1</v>
@@ -3018,37 +3018,37 @@
         <v>6.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
         <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3060,7 +3060,7 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3078,7 +3078,7 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3146,25 +3146,25 @@
         <v>1.22</v>
       </c>
       <c r="G11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
         <v>13.5</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K11" t="n">
         <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
         <v>4.5</v>
@@ -3176,13 +3176,13 @@
         <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
         <v>2.16</v>
@@ -3194,7 +3194,7 @@
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="X11" t="n">
         <v>970</v>
@@ -3209,7 +3209,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AC11" t="n">
         <v>42</v>
@@ -3251,94 +3251,94 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV11" t="n">
         <v>6</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AW11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX11" t="n">
         <v>6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE11" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6</v>
       </c>
       <c r="BF11" t="n">
         <v>4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
@@ -3350,7 +3350,7 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
         <v>5.3</v>
@@ -3409,10 +3409,10 @@
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
@@ -3427,7 +3427,7 @@
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
         <v>1.58</v>
@@ -3436,7 +3436,7 @@
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T12" t="n">
         <v>1.8</v>
@@ -3448,7 +3448,7 @@
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3478,7 +3478,7 @@
         <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
@@ -3499,61 +3499,61 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR12" t="n">
         <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BA12" t="n">
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BG12" t="n">
         <v>4.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -3669,40 +3669,40 @@
         <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.55</v>
       </c>
       <c r="U13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3714,10 +3714,10 @@
         <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
         <v>42</v>
@@ -3729,7 +3729,7 @@
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3741,7 +3741,7 @@
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
         <v>970</v>
@@ -3753,22 +3753,22 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="AO13" t="n">
         <v>600</v>
       </c>
       <c r="AP13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AR13" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3777,10 +3777,10 @@
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3789,34 +3789,34 @@
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
         <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
         <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.199999999999999</v>
@@ -3831,10 +3831,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
@@ -3846,19 +3846,19 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
         <v>2.52</v>
@@ -3923,46 +3923,46 @@
         <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
         <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
         <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>970</v>
@@ -3974,7 +3974,7 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
         <v>500</v>
@@ -4022,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
         <v>8.4</v>
@@ -4037,7 +4037,7 @@
         <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
@@ -4046,25 +4046,25 @@
         <v>8.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BF14" t="n">
         <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BH14" t="n">
         <v>3.85</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -4159,76 +4159,76 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>4.1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="V15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
         <v>25</v>
       </c>
       <c r="AB15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
         <v>11.5</v>
@@ -4240,31 +4240,31 @@
         <v>34</v>
       </c>
       <c r="AG15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP15" t="n">
         <v>11.5</v>
@@ -4273,13 +4273,13 @@
         <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
         <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="n">
         <v>9</v>
@@ -4303,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
@@ -4315,74 +4315,74 @@
         <v>23</v>
       </c>
       <c r="BF15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO15" t="n">
         <v>5.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ15" t="n">
         <v>7</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BS15" t="n">
         <v>7.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BU15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BV15" t="n">
         <v>13.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA15" t="n">
         <v>5.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -4419,79 +4419,79 @@
         <v>2.92</v>
       </c>
       <c r="H16" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
         <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.69</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.59</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>80</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -4506,7 +4506,7 @@
         <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -4521,28 +4521,28 @@
         <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -4551,67 +4551,67 @@
         <v>6.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
         <v>3</v>
       </c>
-      <c r="BF16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG16" t="n">
+      <c r="BN16" t="n">
         <v>6</v>
       </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.51</v>
+        <v>8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU16" t="n">
         <v>4.5</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.51</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.48</v>
+        <v>8.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
         <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
@@ -4700,13 +4700,13 @@
         <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T17" t="n">
         <v>2.02</v>
@@ -4745,37 +4745,37 @@
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK17" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AL17" t="n">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AO17" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
         <v>7.2</v>
@@ -4808,10 +4808,10 @@
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
         <v>20</v>
@@ -4826,7 +4826,7 @@
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="n">
         <v>2.88</v>
@@ -4850,7 +4850,7 @@
         <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>4.5</v>
@@ -4942,7 +4942,7 @@
         <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
         <v>4.4</v>
@@ -4951,34 +4951,34 @@
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="X18" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -4987,34 +4987,34 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
@@ -5023,22 +5023,22 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
         <v>5.8</v>
@@ -5047,104 +5047,104 @@
         <v>5.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AY18" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="BB18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH18" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -5175,31 +5175,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="G19" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
         <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
@@ -5208,13 +5208,13 @@
         <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
         <v>1.74</v>
@@ -5223,10 +5223,10 @@
         <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -5429,196 +5429,196 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="G20" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K20" t="n">
         <v>5.9</v>
       </c>
-      <c r="K20" t="n">
-        <v>6.8</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="n">
-        <v>460</v>
+        <v>310</v>
       </c>
       <c r="AB20" t="n">
         <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AE20" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>65</v>
       </c>
       <c r="AI20" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="AJ20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO20" t="n">
         <v>160</v>
       </c>
-      <c r="AN20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>260</v>
-      </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY20" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
       </c>
       <c r="BD20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG20" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BR20" t="n">
         <v>23</v>
@@ -5627,10 +5627,10 @@
         <v>6.8</v>
       </c>
       <c r="BT20" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5645,14 +5645,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J21" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="K21" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
@@ -5710,64 +5710,64 @@
         <v>7.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S21" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T21" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="Z21" t="n">
         <v>450</v>
       </c>
       <c r="AA21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD21" t="n">
         <v>34</v>
       </c>
       <c r="AE21" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="AF21" t="n">
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AI21" t="n">
         <v>320</v>
@@ -5776,10 +5776,10 @@
         <v>16.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
         <v>260</v>
@@ -5788,46 +5788,46 @@
         <v>5</v>
       </c>
       <c r="AO21" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
         <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>11.5</v>
@@ -5839,13 +5839,13 @@
         <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>65</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BI21" t="n">
         <v>4.1</v>
@@ -5854,13 +5854,13 @@
         <v>9.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.7</v>
@@ -5872,41 +5872,41 @@
         <v>8.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
         <v>2.72</v>
@@ -5946,16 +5946,16 @@
         <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -5979,13 +5979,13 @@
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
         <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.58</v>
@@ -5997,7 +5997,7 @@
         <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
         <v>150</v>
@@ -6036,7 +6036,7 @@
         <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>30</v>
@@ -6054,7 +6054,7 @@
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT22" t="n">
         <v>6.8</v>
@@ -6066,7 +6066,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX22" t="n">
         <v>11.5</v>
@@ -6078,89 +6078,89 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD22" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>7.2</v>
       </c>
       <c r="BE22" t="n">
         <v>8</v>
       </c>
       <c r="BF22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT22" t="n">
         <v>6.6</v>
       </c>
-      <c r="BG22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU22" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -6191,46 +6191,46 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S23" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6245,7 +6245,7 @@
         <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y23" t="n">
         <v>950</v>
@@ -6260,7 +6260,7 @@
         <v>950</v>
       </c>
       <c r="AC23" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD23" t="n">
         <v>950</v>
@@ -6278,7 +6278,7 @@
         <v>950</v>
       </c>
       <c r="AI23" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
         <v>900</v>
@@ -6293,10 +6293,10 @@
         <v>500</v>
       </c>
       <c r="AN23" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO23" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP23" t="n">
         <v>4.2</v>
@@ -6305,10 +6305,10 @@
         <v>6.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AT23" t="n">
         <v>4.2</v>
@@ -6317,34 +6317,34 @@
         <v>3.85</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="BF23" t="n">
         <v>1.55</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H24" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J24" t="n">
         <v>3.5</v>
@@ -6463,34 +6463,34 @@
         <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -6505,19 +6505,19 @@
         <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AA24" t="n">
         <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
         <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
         <v>500</v>
@@ -6526,7 +6526,7 @@
         <v>28</v>
       </c>
       <c r="AG24" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AH24" t="n">
         <v>34</v>
@@ -6547,25 +6547,25 @@
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AO24" t="n">
         <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
         <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
@@ -6577,7 +6577,7 @@
         <v>17.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AY24" t="n">
         <v>11.5</v>
@@ -6586,22 +6586,22 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG24" t="n">
         <v>12.5</v>
@@ -6610,19 +6610,19 @@
         <v>3.65</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6631,44 +6631,44 @@
         <v>5.4</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU24" t="n">
         <v>4</v>
       </c>
       <c r="BV24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
         <v>7.6</v>
       </c>
-      <c r="BZ24" t="n">
-        <v>26</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G25" t="n">
         <v>8.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="I25" t="n">
         <v>1.62</v>
@@ -6714,34 +6714,34 @@
         <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>1.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
         <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
         <v>1.63</v>
@@ -6753,7 +6753,7 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
         <v>6.2</v>
@@ -6768,7 +6768,7 @@
         <v>29</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD25" t="n">
         <v>11</v>
@@ -6807,10 +6807,10 @@
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR25" t="n">
         <v>6.2</v>
@@ -6825,10 +6825,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX25" t="n">
         <v>20</v>
@@ -6837,31 +6837,31 @@
         <v>25</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
         <v>10</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI25" t="n">
         <v>2.48</v>
@@ -6870,34 +6870,34 @@
         <v>13.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN25" t="n">
         <v>12</v>
       </c>
       <c r="BO25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU25" t="n">
         <v>3.05</v>
@@ -6906,23 +6906,23 @@
         <v>11.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BX25" t="n">
         <v>38</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA25" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
@@ -7240,7 +7240,7 @@
         <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -7291,10 +7291,10 @@
         <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
         <v>22</v>
@@ -7306,7 +7306,7 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>17</v>
@@ -7318,7 +7318,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR27" t="n">
         <v>30</v>
@@ -7336,7 +7336,7 @@
         <v>15.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
@@ -7345,7 +7345,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
         <v>60</v>
@@ -7354,16 +7354,16 @@
         <v>19</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD27" t="n">
         <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG27" t="n">
         <v>12.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -7464,16 +7464,16 @@
         <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="H28" t="n">
         <v>2.26</v>
       </c>
       <c r="I28" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>4.1</v>
@@ -7485,55 +7485,55 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
         <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y28" t="n">
         <v>500</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>16</v>
       </c>
       <c r="Z28" t="n">
         <v>970</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB28" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="AC28" t="n">
         <v>14</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE28" t="n">
         <v>500</v>
@@ -7578,10 +7578,10 @@
         <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -7590,10 +7590,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
@@ -7602,25 +7602,25 @@
         <v>11.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
         <v>5.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH28" t="n">
         <v>5.5</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
@@ -7650,13 +7650,13 @@
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
@@ -7674,17 +7674,17 @@
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -7718,28 +7718,28 @@
         <v>1.73</v>
       </c>
       <c r="G29" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I29" t="n">
         <v>6.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.4</v>
@@ -7748,7 +7748,7 @@
         <v>1.69</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
         <v>1.26</v>
@@ -7760,13 +7760,13 @@
         <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X29" t="n">
         <v>12</v>
@@ -7784,13 +7784,13 @@
         <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
         <v>24</v>
       </c>
       <c r="AE29" t="n">
-        <v>260</v>
+        <v>470</v>
       </c>
       <c r="AF29" t="n">
         <v>10.5</v>
@@ -7829,25 +7829,25 @@
         <v>13.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU29" t="n">
         <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY29" t="n">
         <v>8.800000000000001</v>
@@ -7856,25 +7856,25 @@
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
         <v>13</v>
       </c>
       <c r="BG29" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH29" t="n">
         <v>3.15</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G30" t="n">
         <v>2.26</v>
       </c>
       <c r="H30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I30" t="n">
         <v>4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>3.25</v>
@@ -7993,31 +7993,31 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
         <v>1.78</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U30" t="n">
         <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
         <v>1.79</v>
@@ -8035,7 +8035,7 @@
         <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC30" t="n">
         <v>7.2</v>
@@ -8065,16 +8065,16 @@
         <v>27</v>
       </c>
       <c r="AL30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM30" t="n">
         <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO30" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP30" t="n">
         <v>9.800000000000001</v>
@@ -8086,7 +8086,7 @@
         <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -8095,25 +8095,25 @@
         <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW30" t="n">
         <v>46</v>
       </c>
       <c r="AX30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC30" t="n">
         <v>23</v>
@@ -8122,10 +8122,10 @@
         <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BF30" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG30" t="n">
         <v>50</v>
@@ -8140,7 +8140,7 @@
         <v>11</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8149,7 +8149,7 @@
         <v>10</v>
       </c>
       <c r="BN30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO30" t="n">
         <v>4.2</v>
@@ -8158,13 +8158,13 @@
         <v>18</v>
       </c>
       <c r="BQ30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR30" t="n">
         <v>36</v>
       </c>
       <c r="BS30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT30" t="n">
         <v>7.2</v>
@@ -8176,23 +8176,23 @@
         <v>36</v>
       </c>
       <c r="BW30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ30" t="n">
         <v>36</v>
       </c>
       <c r="CA30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -8223,58 +8223,58 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="G31" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H31" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K31" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="R31" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="T31" t="n">
         <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X31" t="n">
         <v>950</v>
@@ -8316,7 +8316,7 @@
         <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -8331,16 +8331,16 @@
         <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR31" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="AT31" t="n">
         <v>6.4</v>
@@ -8349,46 +8349,46 @@
         <v>5.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AX31" t="n">
         <v>7</v>
       </c>
       <c r="AY31" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ31" t="n">
         <v>10.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="BF31" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG31" t="n">
         <v>7</v>
       </c>
       <c r="BH31" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
@@ -8400,7 +8400,7 @@
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
@@ -8418,7 +8418,7 @@
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
@@ -8430,13 +8430,13 @@
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H32" t="n">
         <v>3.3</v>
@@ -8516,7 +8516,7 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
         <v>2.2</v>
@@ -8528,10 +8528,10 @@
         <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X32" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y32" t="n">
         <v>10.5</v>
@@ -8549,13 +8549,13 @@
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE32" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF32" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG32" t="n">
         <v>15.5</v>
@@ -8564,7 +8564,7 @@
         <v>29</v>
       </c>
       <c r="AI32" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AJ32" t="n">
         <v>46</v>
@@ -8594,19 +8594,19 @@
         <v>17</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT32" t="n">
         <v>5.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AV32" t="n">
         <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AX32" t="n">
         <v>11.5</v>
@@ -8618,25 +8618,25 @@
         <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH32" t="n">
         <v>2.6</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -8734,22 +8734,22 @@
         <v>2.08</v>
       </c>
       <c r="G33" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H33" t="n">
         <v>3.95</v>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
         <v>1.1</v>
@@ -8761,7 +8761,7 @@
         <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
         <v>2.3</v>
@@ -8773,22 +8773,22 @@
         <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y33" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="n">
         <v>500</v>
@@ -8797,164 +8797,164 @@
         <v>900</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AE33" t="n">
         <v>500</v>
       </c>
       <c r="AF33" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="AH33" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI33" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AJ33" t="n">
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
       </c>
       <c r="AM33" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AO33" t="n">
         <v>500</v>
       </c>
       <c r="AP33" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="AT33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK33" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>2.98</v>
+        <v>12.5</v>
       </c>
       <c r="BN33" t="n">
         <v>4.7</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -8988,16 +8988,16 @@
         <v>1.92</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I34" t="n">
         <v>5.5</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K34" t="n">
         <v>3.55</v>
@@ -9009,16 +9009,16 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R34" t="n">
         <v>1.19</v>
@@ -9039,13 +9039,13 @@
         <v>1.86</v>
       </c>
       <c r="X34" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA34" t="n">
         <v>900</v>
@@ -9054,13 +9054,13 @@
         <v>7.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD34" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE34" t="n">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="AF34" t="n">
         <v>12</v>
@@ -9069,10 +9069,10 @@
         <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI34" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AJ34" t="n">
         <v>27</v>
@@ -9081,70 +9081,70 @@
         <v>29</v>
       </c>
       <c r="AL34" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM34" t="n">
         <v>500</v>
       </c>
       <c r="AN34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO34" t="n">
         <v>700</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX34" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF34" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BH34" t="n">
         <v>2.88</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,75 +843,75 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Juventud Unida San Miguel</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="S2" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -938,156 +938,156 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,69 +1097,69 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.02</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.54</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1168,180 +1168,180 @@
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.91</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.08</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>95</v>
+        <v>2.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>290</v>
+        <v>15.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="AR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG4" t="n">
         <v>7.6</v>
       </c>
-      <c r="AS4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>36</v>
-      </c>
       <c r="BH4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,114 +1605,114 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AD Berazategui</t>
+          <t>Real San Joaquin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Juventud Unida San Miguel</t>
+          <t>Concon National FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>75</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>1.26</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.32</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>28</v>
+        <v>1.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>220</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AD5" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1721,135 +1721,135 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.76</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.96</v>
+        <v>17.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.76</v>
+        <v>120</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.34</v>
+        <v>40</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.5</v>
+        <v>100</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.44</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.76</v>
+        <v>14.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.56</v>
+        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,64 +1864,64 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CD General Velasquez</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>1.24</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>60</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1930,34 +1930,34 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF6" t="n">
         <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1978,132 +1978,132 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>180</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>2.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>4.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.18</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>1.82</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>7.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>1.77</v>
       </c>
       <c r="AR7" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>20</v>
       </c>
-      <c r="AT7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AW7" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>100</v>
       </c>
       <c r="BA7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>17</v>
+        <v>220</v>
       </c>
       <c r="BD7" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="BE7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="BG7" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Real San Joaquin</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Concon National FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>2.86</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.08</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.29</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.63</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA8" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>30</v>
       </c>
-      <c r="BB8" t="n">
-        <v>36</v>
-      </c>
       <c r="BC8" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="BF8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BG8" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD General Velasquez</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AM9" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="AO9" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="BF9" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BG9" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
         <v>12</v>
       </c>
-      <c r="BN9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR9" t="n">
+      <c r="BT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV9" t="n">
         <v>34</v>
       </c>
-      <c r="BS9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>60</v>
-      </c>
       <c r="BW9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.51</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
         <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>370</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>11</v>
       </c>
-      <c r="AH10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AR10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW10" t="n">
         <v>30</v>
       </c>
-      <c r="AK10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>46</v>
-      </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BB10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
         <v>100</v>
       </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BG10" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BH10" t="n">
         <v>2.96</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
         <v>130</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>3.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>12.5</v>
+        <v>3.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>36</v>
       </c>
       <c r="CA10" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,1006 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="X11" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z11" t="n">
         <v>42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>100</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM11" t="n">
         <v>500</v>
       </c>
-      <c r="AF11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
         <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BU11" t="n">
         <v>7</v>
       </c>
-      <c r="BB11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC11" t="n">
+      <c r="BV11" t="n">
+        <v>90</v>
+      </c>
+      <c r="BW11" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.66</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Tacuarembo</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Uruguay Montevideo FC</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>540</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-06-07 15:32:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Defensor Sporting</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Boston River</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>370</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>130</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-07 15:32:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Venezuelan Primera Division</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Carabobo FC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Puerto Cabello</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,769 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tacuarembo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Uruguay Montevideo FC</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>150</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S3" t="n">
-        <v>430</v>
-      </c>
-      <c r="T3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-07 19:48:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Defensor Sporting</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Boston River</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>250</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>400</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>120</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>340</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>120</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>160</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>390</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-07 19:48:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Venezuelan Primera Division</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Carabobo FC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Puerto Cabello</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>220</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>140</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>250</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>220</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>880</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
